--- a/ROSA_vitaSPEC/Results/test_pretraitements/trans.beta.carotenes/Resultats_trans.beta.carotenes_moy_diff.xlsx
+++ b/ROSA_vitaSPEC/Results/test_pretraitements/trans.beta.carotenes/Resultats_trans.beta.carotenes_moy_diff.xlsx
@@ -1,217 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\U108-N806\Documents\STAGE_M2_ROSA_NIRS\VitaSPEC\vitaspec_R\ROSA_vitaSPEC\Results\test_pretraitements\trans.beta.carotenes\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
-  <si>
-    <t>Pretraitement</t>
-  </si>
-  <si>
-    <t>LV1_diff</t>
-  </si>
-  <si>
-    <t>LV2_diff</t>
-  </si>
-  <si>
-    <t>LV3_diff</t>
-  </si>
-  <si>
-    <t>LV4_diff</t>
-  </si>
-  <si>
-    <t>LV5_diff</t>
-  </si>
-  <si>
-    <t>LV6_diff</t>
-  </si>
-  <si>
-    <t>LV7_diff</t>
-  </si>
-  <si>
-    <t>LV8_diff</t>
-  </si>
-  <si>
-    <t>LV9_diff</t>
-  </si>
-  <si>
-    <t>LV10_diff</t>
-  </si>
-  <si>
-    <t>LV11_diff</t>
-  </si>
-  <si>
-    <t>LV12_diff</t>
-  </si>
-  <si>
-    <t>LV13_diff</t>
-  </si>
-  <si>
-    <t>LV14_diff</t>
-  </si>
-  <si>
-    <t>LV15_diff</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1000,1)_snv_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1200,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_msc_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,25)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,9)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,25)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1400,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(40,1300,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(950,20,1)_snv_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(950,20,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(950,750,1)_snv_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(950,750,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_msc_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,21)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,25)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,27)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,31)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,17)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,19)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,25)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(2,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_snv_sder_c(1,3,5)_</t>
-  </si>
-  <si>
-    <t>adj_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>snv_sder_c(1,3,9)_red_c(10,10,1)_</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -223,13 +27,6 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -255,82 +52,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -372,7 +109,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -404,10 +141,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -439,7 +175,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -615,2373 +350,2485 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:P47"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="52.5703125" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>16</v>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Pretraitement</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>LV1_diff</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>LV2_diff</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>LV3_diff</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>LV4_diff</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>LV5_diff</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>LV6_diff</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>LV7_diff</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>LV8_diff</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>LV9_diff</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>LV10_diff</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>LV11_diff</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>LV12_diff</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>LV13_diff</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>LV14_diff</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>LV15_diff</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1000,1)_snv_</t>
+        </is>
       </c>
       <c r="B2">
-        <v>3.9741484773253899E-2</v>
+        <v>0.03925080979722251</v>
       </c>
       <c r="C2">
-        <v>6.3278729457387772E-2</v>
+        <v>0.05951201704284392</v>
       </c>
       <c r="D2">
-        <v>8.8119431887994315E-2</v>
+        <v>0.08419574319673762</v>
       </c>
       <c r="E2">
-        <v>8.5805213899972643E-2</v>
+        <v>0.08482486876791973</v>
       </c>
       <c r="F2">
-        <v>0.12903360953272691</v>
+        <v>0.1303373343065161</v>
       </c>
       <c r="G2">
-        <v>0.13967500575930261</v>
+        <v>0.134694465623883</v>
       </c>
       <c r="H2">
-        <v>0.1671565334937275</v>
+        <v>0.1627288312272666</v>
       </c>
       <c r="I2">
-        <v>0.17640781829336941</v>
+        <v>0.1725318156769989</v>
       </c>
       <c r="J2">
-        <v>0.1878286711833124</v>
+        <v>0.1874276260016305</v>
       </c>
       <c r="K2">
-        <v>0.2042177829247763</v>
+        <v>0.2000451461052175</v>
       </c>
       <c r="L2">
-        <v>0.26658365642844578</v>
+        <v>0.2626506034022283</v>
       </c>
       <c r="M2">
-        <v>0.31833786832083028</v>
+        <v>0.3173969996726505</v>
       </c>
       <c r="N2">
-        <v>0.38514350727232338</v>
+        <v>0.3827254220485842</v>
       </c>
       <c r="O2">
-        <v>0.47106544178507259</v>
+        <v>0.4719946906815988</v>
       </c>
       <c r="P2">
-        <v>0.45098435953475258</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>17</v>
+        <v>0.4524490853042606</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1200,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B3">
-        <v>4.2025223081861303E-2</v>
+        <v>0.04294674602846288</v>
       </c>
       <c r="C3">
-        <v>4.2566050478394457E-2</v>
+        <v>0.04205930974970762</v>
       </c>
       <c r="D3">
-        <v>8.6838377030244995E-2</v>
+        <v>0.08483002268621315</v>
       </c>
       <c r="E3">
-        <v>0.11731983867327871</v>
+        <v>0.1144025217580288</v>
       </c>
       <c r="F3">
-        <v>0.15554036448900721</v>
+        <v>0.1517597196648307</v>
       </c>
       <c r="G3">
-        <v>0.18496605933636009</v>
+        <v>0.1769747533443988</v>
       </c>
       <c r="H3">
-        <v>0.24137563019196159</v>
+        <v>0.2341622105284624</v>
       </c>
       <c r="I3">
-        <v>0.27397630406988749</v>
+        <v>0.2704048221196284</v>
       </c>
       <c r="J3">
-        <v>0.30072704761747138</v>
+        <v>0.2977968909713019</v>
       </c>
       <c r="K3">
-        <v>0.33457592306026579</v>
+        <v>0.3330174386050105</v>
       </c>
       <c r="L3">
-        <v>0.39024341857032352</v>
+        <v>0.3870813710755396</v>
       </c>
       <c r="M3">
-        <v>0.49416897390470049</v>
+        <v>0.4859072875142739</v>
       </c>
       <c r="N3">
-        <v>0.60975058263325588</v>
+        <v>0.5996419809989589</v>
       </c>
       <c r="O3">
-        <v>0.67229158817738721</v>
+        <v>0.6657835068568395</v>
       </c>
       <c r="P3">
-        <v>0.74508609692273953</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>18</v>
+        <v>0.7444542645095242</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_msc_</t>
+        </is>
       </c>
       <c r="B4">
-        <v>3.8311361937405967E-2</v>
+        <v>0.03236347096039155</v>
       </c>
       <c r="C4">
-        <v>5.3234809542584083E-2</v>
+        <v>0.04856172701455214</v>
       </c>
       <c r="D4">
-        <v>6.9004892221760594E-2</v>
+        <v>0.06284267916970332</v>
       </c>
       <c r="E4">
-        <v>0.1129360780444771</v>
+        <v>0.1054688130568818</v>
       </c>
       <c r="F4">
-        <v>0.15097151687563751</v>
+        <v>0.1390802253308723</v>
       </c>
       <c r="G4">
-        <v>0.12751301915020349</v>
+        <v>0.115856478181798</v>
       </c>
       <c r="H4">
-        <v>0.12774026285855189</v>
+        <v>0.1188994823897914</v>
       </c>
       <c r="I4">
-        <v>0.17358750884392371</v>
+        <v>0.1619847565208701</v>
       </c>
       <c r="J4">
-        <v>0.2437239470471895</v>
+        <v>0.2317336885886481</v>
       </c>
       <c r="K4">
-        <v>0.30575909608283502</v>
+        <v>0.2997189932092698</v>
       </c>
       <c r="L4">
-        <v>0.43213170734418521</v>
+        <v>0.4220362974277435</v>
       </c>
       <c r="M4">
-        <v>0.43432739845096507</v>
+        <v>0.4273994821259925</v>
       </c>
       <c r="N4">
-        <v>0.42282308229300591</v>
+        <v>0.416132431755197</v>
       </c>
       <c r="O4">
-        <v>0.40836513065669822</v>
+        <v>0.3997421293183803</v>
       </c>
       <c r="P4">
-        <v>0.41639494068253552</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>19</v>
+        <v>0.40640783475848</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B5">
-        <v>3.093594573567993E-2</v>
+        <v>0.03096878236307377</v>
       </c>
       <c r="C5">
-        <v>5.7051325338310088E-2</v>
+        <v>0.05683617715332245</v>
       </c>
       <c r="D5">
-        <v>0.1092727935038101</v>
+        <v>0.1104341840989743</v>
       </c>
       <c r="E5">
-        <v>0.12944816086455749</v>
+        <v>0.1271643288402261</v>
       </c>
       <c r="F5">
-        <v>0.16655511216556279</v>
+        <v>0.1658874103417063</v>
       </c>
       <c r="G5">
-        <v>0.17029368614734541</v>
+        <v>0.1700664147674689</v>
       </c>
       <c r="H5">
-        <v>0.18876709000529779</v>
+        <v>0.1903393406595656</v>
       </c>
       <c r="I5">
-        <v>0.22985640497863341</v>
+        <v>0.2350921924304787</v>
       </c>
       <c r="J5">
-        <v>0.28771645897099629</v>
+        <v>0.2918001644699071</v>
       </c>
       <c r="K5">
-        <v>0.35014412404837769</v>
+        <v>0.352255024314862</v>
       </c>
       <c r="L5">
-        <v>0.4025993624118025</v>
+        <v>0.4167262139524756</v>
       </c>
       <c r="M5">
-        <v>0.45260041704859078</v>
+        <v>0.4653680307631478</v>
       </c>
       <c r="N5">
-        <v>0.44925242165558449</v>
+        <v>0.4581514404512513</v>
       </c>
       <c r="O5">
-        <v>0.45961213022784209</v>
+        <v>0.4736135558459898</v>
       </c>
       <c r="P5">
-        <v>0.45783796511456898</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>20</v>
+        <v>0.4652971805673781</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,21)_</t>
+        </is>
       </c>
       <c r="B6">
-        <v>3.1528481368880479E-2</v>
+        <v>0.02864112477928504</v>
       </c>
       <c r="C6">
-        <v>5.6899434574878997E-2</v>
+        <v>0.05227648530162382</v>
       </c>
       <c r="D6">
-        <v>9.4597572033896404E-2</v>
+        <v>0.09024718345463834</v>
       </c>
       <c r="E6">
-        <v>0.12007569570320439</v>
+        <v>0.1167393749866645</v>
       </c>
       <c r="F6">
-        <v>0.14131110361600191</v>
+        <v>0.1429544020729214</v>
       </c>
       <c r="G6">
-        <v>0.17057925501178309</v>
+        <v>0.1693514613501639</v>
       </c>
       <c r="H6">
-        <v>0.185766949815104</v>
+        <v>0.1869623886884579</v>
       </c>
       <c r="I6">
-        <v>0.251133851005514</v>
+        <v>0.2516699058295379</v>
       </c>
       <c r="J6">
-        <v>0.31796723062828819</v>
+        <v>0.3177674861605148</v>
       </c>
       <c r="K6">
-        <v>0.35432450113130082</v>
+        <v>0.3559252363929205</v>
       </c>
       <c r="L6">
-        <v>0.42159184421713569</v>
+        <v>0.4207369130478037</v>
       </c>
       <c r="M6">
-        <v>0.44895420973316702</v>
+        <v>0.4465295558072203</v>
       </c>
       <c r="N6">
-        <v>0.49897905911951779</v>
+        <v>0.4991205150767337</v>
       </c>
       <c r="O6">
-        <v>0.48701288827886069</v>
+        <v>0.4893347691047588</v>
       </c>
       <c r="P6">
-        <v>0.4903841367134415</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>21</v>
+        <v>0.4849181558729204</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_</t>
+        </is>
       </c>
       <c r="B7">
-        <v>3.6583304617670058E-2</v>
+        <v>0.03621979763616201</v>
       </c>
       <c r="C7">
-        <v>5.2032201999692329E-2</v>
+        <v>0.0512392266310821</v>
       </c>
       <c r="D7">
-        <v>7.9763053426087471E-2</v>
+        <v>0.08256580582571582</v>
       </c>
       <c r="E7">
-        <v>6.7203431510296396E-2</v>
+        <v>0.07007274280824727</v>
       </c>
       <c r="F7">
-        <v>8.9370042331167521E-2</v>
+        <v>0.09288082320735946</v>
       </c>
       <c r="G7">
-        <v>0.1010540308382072</v>
+        <v>0.1031976788625062</v>
       </c>
       <c r="H7">
-        <v>0.13296673819316271</v>
+        <v>0.1320798240066867</v>
       </c>
       <c r="I7">
-        <v>0.14527129376133999</v>
+        <v>0.1424265059736812</v>
       </c>
       <c r="J7">
-        <v>0.18521387379344831</v>
+        <v>0.1820734507461869</v>
       </c>
       <c r="K7">
-        <v>0.25956141826028528</v>
+        <v>0.2499953024739631</v>
       </c>
       <c r="L7">
-        <v>0.31491176893430861</v>
+        <v>0.305883865621826</v>
       </c>
       <c r="M7">
-        <v>0.38075400259621128</v>
+        <v>0.3737282719856718</v>
       </c>
       <c r="N7">
-        <v>0.40023420200000831</v>
+        <v>0.3906952022396313</v>
       </c>
       <c r="O7">
-        <v>0.39674751037356693</v>
+        <v>0.3878928704212097</v>
       </c>
       <c r="P7">
-        <v>0.39112870744477268</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>22</v>
+        <v>0.380016283883086</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_</t>
+        </is>
       </c>
       <c r="B8">
-        <v>3.3545170836416893E-2</v>
+        <v>0.03583396638131192</v>
       </c>
       <c r="C8">
-        <v>5.0345806069816978E-2</v>
+        <v>0.0509986195634235</v>
       </c>
       <c r="D8">
-        <v>7.3874547784183897E-2</v>
+        <v>0.07603291912879651</v>
       </c>
       <c r="E8">
-        <v>9.8556986415098802E-2</v>
+        <v>0.1002973191960008</v>
       </c>
       <c r="F8">
-        <v>0.1084797266280505</v>
+        <v>0.1102478742128374</v>
       </c>
       <c r="G8">
-        <v>0.15525234828670459</v>
+        <v>0.1557453449996075</v>
       </c>
       <c r="H8">
-        <v>0.15215544007034501</v>
+        <v>0.155645753931127</v>
       </c>
       <c r="I8">
-        <v>0.1844863987927178</v>
+        <v>0.1873480091538156</v>
       </c>
       <c r="J8">
-        <v>0.23778737008607839</v>
+        <v>0.2362021480900382</v>
       </c>
       <c r="K8">
-        <v>0.32128498102833319</v>
+        <v>0.320166646409364</v>
       </c>
       <c r="L8">
-        <v>0.41014955116484059</v>
+        <v>0.4103965944896588</v>
       </c>
       <c r="M8">
-        <v>0.42087564934252109</v>
+        <v>0.4249609911047638</v>
       </c>
       <c r="N8">
-        <v>0.40955491437060548</v>
+        <v>0.4138444692159017</v>
       </c>
       <c r="O8">
-        <v>0.39109214891979383</v>
+        <v>0.3973259840454042</v>
       </c>
       <c r="P8">
-        <v>0.419467970633839</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>23</v>
+        <v>0.4261125810277261</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,21)_</t>
+        </is>
       </c>
       <c r="B9">
-        <v>3.2023234683655311E-2</v>
+        <v>0.03128545967092666</v>
       </c>
       <c r="C9">
-        <v>4.9234905123476558E-2</v>
+        <v>0.04627491376612275</v>
       </c>
       <c r="D9">
-        <v>7.6498358511036257E-2</v>
+        <v>0.07076795469399877</v>
       </c>
       <c r="E9">
-        <v>0.100866053192757</v>
+        <v>0.09493577484043914</v>
       </c>
       <c r="F9">
-        <v>0.1106664049243551</v>
+        <v>0.1050932908338237</v>
       </c>
       <c r="G9">
-        <v>0.15401878436130989</v>
+        <v>0.1498888676727641</v>
       </c>
       <c r="H9">
-        <v>0.1511805912958126</v>
+        <v>0.1466783101119326</v>
       </c>
       <c r="I9">
-        <v>0.1743019068654883</v>
+        <v>0.1723948558626897</v>
       </c>
       <c r="J9">
-        <v>0.2005101943262729</v>
+        <v>0.1950591215806495</v>
       </c>
       <c r="K9">
-        <v>0.24542738217956139</v>
+        <v>0.2389724661498718</v>
       </c>
       <c r="L9">
-        <v>0.3252489520739415</v>
+        <v>0.3134832846413961</v>
       </c>
       <c r="M9">
-        <v>0.33873989333506738</v>
+        <v>0.3279225996383513</v>
       </c>
       <c r="N9">
-        <v>0.30820137192860841</v>
+        <v>0.3030218715966179</v>
       </c>
       <c r="O9">
-        <v>0.28900272380984698</v>
+        <v>0.2880862895153334</v>
       </c>
       <c r="P9">
-        <v>0.31691720139681467</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>24</v>
+        <v>0.3128808689613362</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,25)_</t>
+        </is>
       </c>
       <c r="B10">
-        <v>3.3962645474842727E-2</v>
+        <v>0.03665181473539902</v>
       </c>
       <c r="C10">
-        <v>4.9680365153214279E-2</v>
+        <v>0.05628577439261095</v>
       </c>
       <c r="D10">
-        <v>7.7316292485209548E-2</v>
+        <v>0.07953228149322988</v>
       </c>
       <c r="E10">
-        <v>0.1013187725958874</v>
+        <v>0.105798903683309</v>
       </c>
       <c r="F10">
-        <v>0.11142029573432891</v>
+        <v>0.1159180412054788</v>
       </c>
       <c r="G10">
-        <v>0.1557578441421554</v>
+        <v>0.1586367426170208</v>
       </c>
       <c r="H10">
-        <v>0.15334111344564141</v>
+        <v>0.154043078638593</v>
       </c>
       <c r="I10">
-        <v>0.17285184708525261</v>
+        <v>0.1768725918001022</v>
       </c>
       <c r="J10">
-        <v>0.2008772025452559</v>
+        <v>0.201443096085767</v>
       </c>
       <c r="K10">
-        <v>0.23792473479504869</v>
+        <v>0.239559532874127</v>
       </c>
       <c r="L10">
-        <v>0.31770843474264299</v>
+        <v>0.3143263816167946</v>
       </c>
       <c r="M10">
-        <v>0.33035339349072029</v>
+        <v>0.3287255644321678</v>
       </c>
       <c r="N10">
-        <v>0.30243130080066188</v>
+        <v>0.305957899414911</v>
       </c>
       <c r="O10">
-        <v>0.28240170153418748</v>
+        <v>0.2858912772492631</v>
       </c>
       <c r="P10">
-        <v>0.30745762767477769</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>25</v>
+        <v>0.309640969149139</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B11">
-        <v>3.1843507554678192E-2</v>
+        <v>0.02943670343140187</v>
       </c>
       <c r="C11">
-        <v>4.8955007972757369E-2</v>
+        <v>0.04436967871586811</v>
       </c>
       <c r="D11">
-        <v>7.3272582517497131E-2</v>
+        <v>0.06898496834499179</v>
       </c>
       <c r="E11">
-        <v>9.684773272570335E-2</v>
+        <v>0.09178087538883484</v>
       </c>
       <c r="F11">
-        <v>0.10707982765600189</v>
+        <v>0.1018863925885573</v>
       </c>
       <c r="G11">
-        <v>0.14966536547815359</v>
+        <v>0.1447170493603649</v>
       </c>
       <c r="H11">
-        <v>0.14629349703222869</v>
+        <v>0.1420629585734901</v>
       </c>
       <c r="I11">
-        <v>0.16896584504321671</v>
+        <v>0.1643225717168245</v>
       </c>
       <c r="J11">
-        <v>0.19454669665704791</v>
+        <v>0.189513495340914</v>
       </c>
       <c r="K11">
-        <v>0.24115842809720209</v>
+        <v>0.2367625841134867</v>
       </c>
       <c r="L11">
-        <v>0.32219961997698349</v>
+        <v>0.3203474901311356</v>
       </c>
       <c r="M11">
-        <v>0.33658264259741938</v>
+        <v>0.3405171297873616</v>
       </c>
       <c r="N11">
-        <v>0.30896509569411601</v>
+        <v>0.3138036420233187</v>
       </c>
       <c r="O11">
-        <v>0.28838700101680309</v>
+        <v>0.291246229891501</v>
       </c>
       <c r="P11">
-        <v>0.30218203334278121</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>26</v>
+        <v>0.3089807841713521</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B12">
-        <v>3.1438483795426353E-2</v>
+        <v>0.03227910191146749</v>
       </c>
       <c r="C12">
-        <v>5.5610591246457397E-2</v>
+        <v>0.0571366430713196</v>
       </c>
       <c r="D12">
-        <v>0.10671255134044789</v>
+        <v>0.1074900441578888</v>
       </c>
       <c r="E12">
-        <v>0.1104783487890261</v>
+        <v>0.1084015805845076</v>
       </c>
       <c r="F12">
-        <v>0.13562413113976921</v>
+        <v>0.1337629683858551</v>
       </c>
       <c r="G12">
-        <v>0.1550490819017826</v>
+        <v>0.1541274175519359</v>
       </c>
       <c r="H12">
-        <v>0.17652101599921161</v>
+        <v>0.1732071280108399</v>
       </c>
       <c r="I12">
-        <v>0.21072246388476451</v>
+        <v>0.2094265748443052</v>
       </c>
       <c r="J12">
-        <v>0.26329331371461928</v>
+        <v>0.263748530639151</v>
       </c>
       <c r="K12">
-        <v>0.33519393146656618</v>
+        <v>0.3351302321201004</v>
       </c>
       <c r="L12">
-        <v>0.40855464527323299</v>
+        <v>0.4087952561474075</v>
       </c>
       <c r="M12">
-        <v>0.46670271044943412</v>
+        <v>0.4723676211755592</v>
       </c>
       <c r="N12">
-        <v>0.46550620281217459</v>
+        <v>0.4703767073919718</v>
       </c>
       <c r="O12">
-        <v>0.47729895663803151</v>
+        <v>0.4774703295737838</v>
       </c>
       <c r="P12">
-        <v>0.49516058833058002</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>27</v>
+        <v>0.5008781533479849</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,9)_</t>
+        </is>
       </c>
       <c r="B13">
-        <v>3.2476941592598903E-2</v>
+        <v>0.03226257671489213</v>
       </c>
       <c r="C13">
-        <v>6.7275472588083085E-2</v>
+        <v>0.06689624973505282</v>
       </c>
       <c r="D13">
-        <v>0.1149195721921643</v>
+        <v>0.1164728386033281</v>
       </c>
       <c r="E13">
-        <v>0.12766009679776941</v>
+        <v>0.1294380586723682</v>
       </c>
       <c r="F13">
-        <v>0.1546104295201258</v>
+        <v>0.1544373098435285</v>
       </c>
       <c r="G13">
-        <v>0.19039437073988269</v>
+        <v>0.1884425713842328</v>
       </c>
       <c r="H13">
-        <v>0.21656760117418419</v>
+        <v>0.2134520314773207</v>
       </c>
       <c r="I13">
-        <v>0.26327521728640618</v>
+        <v>0.261207526359195</v>
       </c>
       <c r="J13">
-        <v>0.30489401647839809</v>
+        <v>0.3044835498203436</v>
       </c>
       <c r="K13">
-        <v>0.37858780250744251</v>
+        <v>0.3803098622403024</v>
       </c>
       <c r="L13">
-        <v>0.41192076370023312</v>
+        <v>0.4163626656055447</v>
       </c>
       <c r="M13">
-        <v>0.43597875836710548</v>
+        <v>0.4435467860419149</v>
       </c>
       <c r="N13">
-        <v>0.47029763160298388</v>
+        <v>0.4822425263522843</v>
       </c>
       <c r="O13">
-        <v>0.51273041881203585</v>
+        <v>0.5239669208278648</v>
       </c>
       <c r="P13">
-        <v>0.56678815599514243</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>28</v>
+        <v>0.5904013056850499</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
+        </is>
       </c>
       <c r="B14">
-        <v>3.6052194078956767E-2</v>
+        <v>0.03430753391796204</v>
       </c>
       <c r="C14">
-        <v>5.2138053678686458E-2</v>
+        <v>0.04941504576475148</v>
       </c>
       <c r="D14">
-        <v>8.4790949941950577E-2</v>
+        <v>0.07906670358697288</v>
       </c>
       <c r="E14">
-        <v>7.0597650953495794E-2</v>
+        <v>0.06695915744945158</v>
       </c>
       <c r="F14">
-        <v>9.3419698724648725E-2</v>
+        <v>0.08882272339524966</v>
       </c>
       <c r="G14">
-        <v>0.1058049173452488</v>
+        <v>0.09807176259097883</v>
       </c>
       <c r="H14">
-        <v>0.13135755474106281</v>
+        <v>0.1267296877156396</v>
       </c>
       <c r="I14">
-        <v>0.13653544832574169</v>
+        <v>0.1320497700398704</v>
       </c>
       <c r="J14">
-        <v>0.1686728412209472</v>
+        <v>0.1596572304932967</v>
       </c>
       <c r="K14">
-        <v>0.22164271178680889</v>
+        <v>0.2161559016948674</v>
       </c>
       <c r="L14">
-        <v>0.25017270967188993</v>
+        <v>0.2432393929814525</v>
       </c>
       <c r="M14">
-        <v>0.30564537106774509</v>
+        <v>0.3017659433290258</v>
       </c>
       <c r="N14">
-        <v>0.32065836220508981</v>
+        <v>0.323031151503207</v>
       </c>
       <c r="O14">
-        <v>0.31719529558154108</v>
+        <v>0.3213864052022006</v>
       </c>
       <c r="P14">
-        <v>0.29994432858232067</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>29</v>
+        <v>0.3001730599884674</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B15">
-        <v>3.8145124345388359E-2</v>
+        <v>0.0346623879062411</v>
       </c>
       <c r="C15">
-        <v>5.4333172650700812E-2</v>
+        <v>0.05003623571485061</v>
       </c>
       <c r="D15">
-        <v>8.463959339839644E-2</v>
+        <v>0.07951790593534835</v>
       </c>
       <c r="E15">
-        <v>6.8931874747927724E-2</v>
+        <v>0.06873832678699698</v>
       </c>
       <c r="F15">
-        <v>9.1249275026063614E-2</v>
+        <v>0.08976671677226533</v>
       </c>
       <c r="G15">
-        <v>0.1024259976646875</v>
+        <v>0.1005869071332085</v>
       </c>
       <c r="H15">
-        <v>0.1286834382924372</v>
+        <v>0.1250157543323218</v>
       </c>
       <c r="I15">
-        <v>0.1348015639251279</v>
+        <v>0.1310694512821418</v>
       </c>
       <c r="J15">
-        <v>0.164004722450841</v>
+        <v>0.1572898245404964</v>
       </c>
       <c r="K15">
-        <v>0.21916877827261241</v>
+        <v>0.2104285720992844</v>
       </c>
       <c r="L15">
-        <v>0.24527203601917441</v>
+        <v>0.2284066415902615</v>
       </c>
       <c r="M15">
-        <v>0.30294031907089508</v>
+        <v>0.2859105923211259</v>
       </c>
       <c r="N15">
-        <v>0.3189474367491425</v>
+        <v>0.3024514312459178</v>
       </c>
       <c r="O15">
-        <v>0.31605688707405649</v>
+        <v>0.3021925983053839</v>
       </c>
       <c r="P15">
-        <v>0.30095484686272128</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>30</v>
+        <v>0.2845494905238056</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,25)_</t>
+        </is>
       </c>
       <c r="B16">
-        <v>3.4853559457550198E-2</v>
+        <v>0.0327787821513848</v>
       </c>
       <c r="C16">
-        <v>4.9695172428694652E-2</v>
+        <v>0.04878739185809938</v>
       </c>
       <c r="D16">
-        <v>7.7335430412063255E-2</v>
+        <v>0.07745732681823869</v>
       </c>
       <c r="E16">
-        <v>6.5777733285445894E-2</v>
+        <v>0.06456030588142592</v>
       </c>
       <c r="F16">
-        <v>8.7133736853092891E-2</v>
+        <v>0.08511764570534375</v>
       </c>
       <c r="G16">
-        <v>9.7684524626277858E-2</v>
+        <v>0.09829545132143391</v>
       </c>
       <c r="H16">
-        <v>0.12557409200498221</v>
+        <v>0.1217516594706405</v>
       </c>
       <c r="I16">
-        <v>0.1309485336087951</v>
+        <v>0.1291428820353633</v>
       </c>
       <c r="J16">
-        <v>0.15931264664072331</v>
+        <v>0.1557803987430372</v>
       </c>
       <c r="K16">
-        <v>0.2139320075465011</v>
+        <v>0.2087556910956744</v>
       </c>
       <c r="L16">
-        <v>0.23506686233301621</v>
+        <v>0.2278916276802081</v>
       </c>
       <c r="M16">
-        <v>0.28796273083173901</v>
+        <v>0.2781284983387365</v>
       </c>
       <c r="N16">
-        <v>0.3143986305745175</v>
+        <v>0.2988771947460988</v>
       </c>
       <c r="O16">
-        <v>0.31008607748029821</v>
+        <v>0.3035055641278729</v>
       </c>
       <c r="P16">
-        <v>0.29317430826363639</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>31</v>
+        <v>0.2901309412524014</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
+        </is>
       </c>
       <c r="B17">
-        <v>3.3352300395135093E-2</v>
+        <v>0.03614674951309643</v>
       </c>
       <c r="C17">
-        <v>5.0043832326749693E-2</v>
+        <v>0.05065745800114996</v>
       </c>
       <c r="D17">
-        <v>8.133578449068446E-2</v>
+        <v>0.08061808282425798</v>
       </c>
       <c r="E17">
-        <v>6.8855955784755007E-2</v>
+        <v>0.06632991454775228</v>
       </c>
       <c r="F17">
-        <v>9.1797370282456159E-2</v>
+        <v>0.08669905217807261</v>
       </c>
       <c r="G17">
-        <v>0.1024560106070569</v>
+        <v>0.09798770738570761</v>
       </c>
       <c r="H17">
-        <v>0.1298662126938683</v>
+        <v>0.1233958400987966</v>
       </c>
       <c r="I17">
-        <v>0.13454462135628409</v>
+        <v>0.1283999958906622</v>
       </c>
       <c r="J17">
-        <v>0.16342570337537091</v>
+        <v>0.1561862466078274</v>
       </c>
       <c r="K17">
-        <v>0.21582433224590269</v>
+        <v>0.20739115445182</v>
       </c>
       <c r="L17">
-        <v>0.2366992456164525</v>
+        <v>0.2264544256150591</v>
       </c>
       <c r="M17">
-        <v>0.28806503798144151</v>
+        <v>0.2662229235095057</v>
       </c>
       <c r="N17">
-        <v>0.30685023195183242</v>
+        <v>0.2835693561789163</v>
       </c>
       <c r="O17">
-        <v>0.30114499516002308</v>
+        <v>0.276871010846737</v>
       </c>
       <c r="P17">
-        <v>0.28963724642158167</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>32</v>
+        <v>0.2709782279397898</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B18">
-        <v>3.0952536187268339E-2</v>
+        <v>0.0319073309725959</v>
       </c>
       <c r="C18">
-        <v>6.1732331825287923E-2</v>
+        <v>0.05979851456119289</v>
       </c>
       <c r="D18">
-        <v>0.11072477151819531</v>
+        <v>0.1071509982320693</v>
       </c>
       <c r="E18">
-        <v>0.1186760532746763</v>
+        <v>0.1160620794776579</v>
       </c>
       <c r="F18">
-        <v>0.1412496540398106</v>
+        <v>0.1370129515582076</v>
       </c>
       <c r="G18">
-        <v>0.16328216169244719</v>
+        <v>0.1596653291197236</v>
       </c>
       <c r="H18">
-        <v>0.17565830543643099</v>
+        <v>0.1713454005269129</v>
       </c>
       <c r="I18">
-        <v>0.23638217203658959</v>
+        <v>0.2320610588348728</v>
       </c>
       <c r="J18">
-        <v>0.26530348191733572</v>
+        <v>0.2627860810297378</v>
       </c>
       <c r="K18">
-        <v>0.32481611536813149</v>
+        <v>0.3260039438165981</v>
       </c>
       <c r="L18">
-        <v>0.37823939763736708</v>
+        <v>0.3780765359445445</v>
       </c>
       <c r="M18">
-        <v>0.42080329987326831</v>
+        <v>0.4205877085681947</v>
       </c>
       <c r="N18">
-        <v>0.41194480108682507</v>
+        <v>0.4121876906756433</v>
       </c>
       <c r="O18">
-        <v>0.41989356169425501</v>
+        <v>0.4207856371956402</v>
       </c>
       <c r="P18">
-        <v>0.43256737438688281</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>33</v>
+        <v>0.4281644902431649</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,21)_</t>
+        </is>
       </c>
       <c r="B19">
-        <v>3.035442030690794E-2</v>
+        <v>0.03275501264246605</v>
       </c>
       <c r="C19">
-        <v>5.6959063022342993E-2</v>
+        <v>0.06100486814501305</v>
       </c>
       <c r="D19">
-        <v>9.1295258918810074E-2</v>
+        <v>0.09520401679555546</v>
       </c>
       <c r="E19">
-        <v>0.10817361215068</v>
+        <v>0.114180525409694</v>
       </c>
       <c r="F19">
-        <v>0.1250386539893148</v>
+        <v>0.1317350861605663</v>
       </c>
       <c r="G19">
-        <v>0.14146025389300659</v>
+        <v>0.1512297880962825</v>
       </c>
       <c r="H19">
-        <v>0.15916984848558741</v>
+        <v>0.1730274833763141</v>
       </c>
       <c r="I19">
-        <v>0.204773126035078</v>
+        <v>0.2207922891490931</v>
       </c>
       <c r="J19">
-        <v>0.27487380373679399</v>
+        <v>0.2915046888700138</v>
       </c>
       <c r="K19">
-        <v>0.32267165126328001</v>
+        <v>0.3392892060814803</v>
       </c>
       <c r="L19">
-        <v>0.37337712732501321</v>
+        <v>0.3885858523277236</v>
       </c>
       <c r="M19">
-        <v>0.37768891734055038</v>
+        <v>0.3921029182176735</v>
       </c>
       <c r="N19">
-        <v>0.39461071940624393</v>
+        <v>0.4054916861272432</v>
       </c>
       <c r="O19">
-        <v>0.3924661644256609</v>
+        <v>0.4030202380163012</v>
       </c>
       <c r="P19">
-        <v>0.41849484198590359</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>34</v>
+        <v>0.4323610673763688</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
+        </is>
       </c>
       <c r="B20">
-        <v>2.7756225391481589E-2</v>
+        <v>0.03084336557175582</v>
       </c>
       <c r="C20">
-        <v>5.286835469683715E-2</v>
+        <v>0.06005782561826301</v>
       </c>
       <c r="D20">
-        <v>8.2371442689502583E-2</v>
+        <v>0.09227459172989705</v>
       </c>
       <c r="E20">
-        <v>0.1248136912015075</v>
+        <v>0.136117892113841</v>
       </c>
       <c r="F20">
-        <v>0.12532975133362839</v>
+        <v>0.13439823411448</v>
       </c>
       <c r="G20">
-        <v>0.13647308025060589</v>
+        <v>0.1426132917346862</v>
       </c>
       <c r="H20">
-        <v>0.16476994834184189</v>
+        <v>0.1709774612463444</v>
       </c>
       <c r="I20">
-        <v>0.19589801662945011</v>
+        <v>0.2048710335545614</v>
       </c>
       <c r="J20">
-        <v>0.2665050717036036</v>
+        <v>0.2737935980224332</v>
       </c>
       <c r="K20">
-        <v>0.32719290912310878</v>
+        <v>0.3293824661094373</v>
       </c>
       <c r="L20">
-        <v>0.34355898039570648</v>
+        <v>0.3444615435184774</v>
       </c>
       <c r="M20">
-        <v>0.34507106538338161</v>
+        <v>0.3402073079652561</v>
       </c>
       <c r="N20">
-        <v>0.36273032592487758</v>
+        <v>0.3549549218886719</v>
       </c>
       <c r="O20">
-        <v>0.34570032256522132</v>
+        <v>0.3378435393218049</v>
       </c>
       <c r="P20">
-        <v>0.38231955849204352</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>35</v>
+        <v>0.3769337016491001</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B21">
-        <v>4.0252704863570077E-2</v>
+        <v>0.04254236831502756</v>
       </c>
       <c r="C21">
-        <v>4.2033082257860621E-2</v>
+        <v>0.04179841366380704</v>
       </c>
       <c r="D21">
-        <v>8.065908466462296E-2</v>
+        <v>0.07749664378775128</v>
       </c>
       <c r="E21">
-        <v>0.1106833248283018</v>
+        <v>0.1034109607640937</v>
       </c>
       <c r="F21">
-        <v>0.14513039327417329</v>
+        <v>0.1371336632970988</v>
       </c>
       <c r="G21">
-        <v>0.17807875988785921</v>
+        <v>0.172886586205347</v>
       </c>
       <c r="H21">
-        <v>0.26602351026061738</v>
+        <v>0.2539851607829859</v>
       </c>
       <c r="I21">
-        <v>0.32300007526414481</v>
+        <v>0.3136367807468124</v>
       </c>
       <c r="J21">
-        <v>0.35554664429960958</v>
+        <v>0.35620240838857</v>
       </c>
       <c r="K21">
-        <v>0.40741639905140981</v>
+        <v>0.4055770705669217</v>
       </c>
       <c r="L21">
-        <v>0.44854623515634839</v>
+        <v>0.446974599225591</v>
       </c>
       <c r="M21">
-        <v>0.52986304547837948</v>
+        <v>0.5239416795064709</v>
       </c>
       <c r="N21">
-        <v>0.60754975972193448</v>
+        <v>0.6003204334720016</v>
       </c>
       <c r="O21">
-        <v>0.68442796187233335</v>
+        <v>0.6787852415818958</v>
       </c>
       <c r="P21">
-        <v>0.8107595817940938</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>36</v>
+        <v>0.8014467093326396</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1400,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B22">
-        <v>4.1360143843544472E-2</v>
+        <v>0.03986557118729472</v>
       </c>
       <c r="C22">
-        <v>4.239400369062607E-2</v>
+        <v>0.04094917378914087</v>
       </c>
       <c r="D22">
-        <v>7.7054247265245124E-2</v>
+        <v>0.07639736239498451</v>
       </c>
       <c r="E22">
-        <v>0.1021933773713702</v>
+        <v>0.1037074096793711</v>
       </c>
       <c r="F22">
-        <v>0.14492035659444211</v>
+        <v>0.1477156492498897</v>
       </c>
       <c r="G22">
-        <v>0.15397962535481091</v>
+        <v>0.1575849526611391</v>
       </c>
       <c r="H22">
-        <v>0.24837357839786051</v>
+        <v>0.2577068512931724</v>
       </c>
       <c r="I22">
-        <v>0.28995784112553868</v>
+        <v>0.2989271179125701</v>
       </c>
       <c r="J22">
-        <v>0.32003137780666541</v>
+        <v>0.3282702728170293</v>
       </c>
       <c r="K22">
-        <v>0.3740116993945245</v>
+        <v>0.3752178964544692</v>
       </c>
       <c r="L22">
-        <v>0.42860128146871451</v>
+        <v>0.4331508250540173</v>
       </c>
       <c r="M22">
-        <v>0.51579958244145518</v>
+        <v>0.5189539898395932</v>
       </c>
       <c r="N22">
-        <v>0.56600727081791491</v>
+        <v>0.5735306388769179</v>
       </c>
       <c r="O22">
-        <v>0.65261992745763198</v>
+        <v>0.6613484778101766</v>
       </c>
       <c r="P22">
-        <v>0.76681786175832278</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>37</v>
+        <v>0.7799439663121622</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>adj_red_c(40,1300,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B23">
-        <v>3.1047905826071091E-2</v>
+        <v>0.03119579407752027</v>
       </c>
       <c r="C23">
-        <v>7.0434861325004761E-2</v>
+        <v>0.07067335244263828</v>
       </c>
       <c r="D23">
-        <v>8.8155625797714632E-2</v>
+        <v>0.08584484297450035</v>
       </c>
       <c r="E23">
-        <v>9.0653214234180379E-2</v>
+        <v>0.09028116541107645</v>
       </c>
       <c r="F23">
-        <v>0.14605457605823971</v>
+        <v>0.1448728843979217</v>
       </c>
       <c r="G23">
-        <v>0.29828640328123701</v>
+        <v>0.2969840248129894</v>
       </c>
       <c r="H23">
-        <v>0.37205773177215767</v>
+        <v>0.3704374755699263</v>
       </c>
       <c r="I23">
-        <v>0.41254369303938487</v>
+        <v>0.412705742897538</v>
       </c>
       <c r="J23">
-        <v>0.48198962520442062</v>
+        <v>0.481139299971846</v>
       </c>
       <c r="K23">
-        <v>0.5687293062321741</v>
+        <v>0.5634121574544781</v>
       </c>
       <c r="L23">
-        <v>0.6558159806832341</v>
+        <v>0.6507757094894966</v>
       </c>
       <c r="M23">
-        <v>0.76107106635616195</v>
+        <v>0.7639285382772716</v>
       </c>
       <c r="N23">
-        <v>0.8632597099602447</v>
+        <v>0.8618077221279935</v>
       </c>
       <c r="O23">
-        <v>0.95357539468435226</v>
+        <v>0.9532160724685619</v>
       </c>
       <c r="P23">
-        <v>1.1050912879897681</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>38</v>
+        <v>1.101764916474662</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>adj_red_c(950,20,1)_snv_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B24">
-        <v>7.0046268042011722E-2</v>
+        <v>0.06429356992538277</v>
       </c>
       <c r="C24">
-        <v>0.1806487313034362</v>
+        <v>0.1718434889931484</v>
       </c>
       <c r="D24">
-        <v>0.17070923842262689</v>
+        <v>0.1730821548806494</v>
       </c>
       <c r="E24">
-        <v>0.30785638103235091</v>
+        <v>0.3091021483416585</v>
       </c>
       <c r="F24">
-        <v>0.49919821238397633</v>
+        <v>0.4919700525404406</v>
       </c>
       <c r="G24">
-        <v>0.56234056754101103</v>
+        <v>0.5564741237582431</v>
       </c>
       <c r="H24">
-        <v>0.67701695693855857</v>
+        <v>0.6647249290979376</v>
       </c>
       <c r="I24">
-        <v>0.80390355735384122</v>
+        <v>0.7911306317317975</v>
       </c>
       <c r="J24">
-        <v>0.9261656156810969</v>
+        <v>0.9032907030788037</v>
       </c>
       <c r="K24">
-        <v>0.96975118198633847</v>
+        <v>0.9523188662547816</v>
       </c>
       <c r="L24">
-        <v>1.0604670294956029</v>
+        <v>1.038385619123866</v>
       </c>
       <c r="M24">
-        <v>1.1185681157134351</v>
+        <v>1.102437611509808</v>
       </c>
       <c r="N24">
-        <v>1.313761884206702</v>
+        <v>1.284924028405274</v>
       </c>
       <c r="O24">
-        <v>1.405468754274636</v>
+        <v>1.361378212325903</v>
       </c>
       <c r="P24">
-        <v>1.4879748460257971</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>39</v>
+        <v>1.434808037971021</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>adj_red_c(950,20,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B25">
-        <v>8.5878767222116917E-2</v>
+        <v>0.08636863506488909</v>
       </c>
       <c r="C25">
-        <v>0.18648134772994349</v>
+        <v>0.1785058114224123</v>
       </c>
       <c r="D25">
-        <v>0.25112934776763962</v>
+        <v>0.2397124077492794</v>
       </c>
       <c r="E25">
-        <v>0.34149110593288767</v>
+        <v>0.3297735771674824</v>
       </c>
       <c r="F25">
-        <v>0.46631091968817889</v>
+        <v>0.4649681729490988</v>
       </c>
       <c r="G25">
-        <v>0.63771307811265365</v>
+        <v>0.6329866337389809</v>
       </c>
       <c r="H25">
-        <v>0.74007436791512382</v>
+        <v>0.7376679647290628</v>
       </c>
       <c r="I25">
-        <v>0.86471459749119162</v>
+        <v>0.8659693927357853</v>
       </c>
       <c r="J25">
-        <v>0.9454695167043865</v>
+        <v>0.9448898588646131</v>
       </c>
       <c r="K25">
-        <v>1.056696153019413</v>
+        <v>1.052220955310899</v>
       </c>
       <c r="L25">
-        <v>1.1892536295012199</v>
+        <v>1.190903488134985</v>
       </c>
       <c r="M25">
-        <v>1.3196480658522891</v>
+        <v>1.32481382603883</v>
       </c>
       <c r="N25">
-        <v>1.423433019710294</v>
+        <v>1.434815853637472</v>
       </c>
       <c r="O25">
-        <v>1.497780714256822</v>
+        <v>1.514416360579105</v>
       </c>
       <c r="P25">
-        <v>1.545965416291265</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>40</v>
+        <v>1.564469265029184</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>adj_red_c(950,750,1)_snv_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B26">
-        <v>7.0352659180374921E-2</v>
+        <v>0.07099608995203563</v>
       </c>
       <c r="C26">
-        <v>0.13447182959099849</v>
+        <v>0.1305647332914787</v>
       </c>
       <c r="D26">
-        <v>0.15846285464947621</v>
+        <v>0.1538284712387467</v>
       </c>
       <c r="E26">
-        <v>0.20265664640473871</v>
+        <v>0.1957887781132355</v>
       </c>
       <c r="F26">
-        <v>0.31782514449203442</v>
+        <v>0.3066913078030147</v>
       </c>
       <c r="G26">
-        <v>0.3953336815838146</v>
+        <v>0.3848355888006352</v>
       </c>
       <c r="H26">
-        <v>0.53826501602558718</v>
+        <v>0.5275173057631911</v>
       </c>
       <c r="I26">
-        <v>0.61673824629778962</v>
+        <v>0.611490359518164</v>
       </c>
       <c r="J26">
-        <v>0.61723808685801684</v>
+        <v>0.6098319202350806</v>
       </c>
       <c r="K26">
-        <v>0.65247712826810911</v>
+        <v>0.6504318635369117</v>
       </c>
       <c r="L26">
-        <v>0.7391976530667328</v>
+        <v>0.7283879683602493</v>
       </c>
       <c r="M26">
-        <v>0.95504834162247221</v>
+        <v>0.9659049667784367</v>
       </c>
       <c r="N26">
-        <v>0.94225158358544059</v>
+        <v>0.9404901413267803</v>
       </c>
       <c r="O26">
-        <v>0.95746285198537895</v>
+        <v>0.9689610505908364</v>
       </c>
       <c r="P26">
-        <v>0.98928995470908798</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>41</v>
+        <v>0.9798493413630229</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>adj_red_c(950,750,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B27">
-        <v>7.7373948734422535E-2</v>
+        <v>0.08293828495322139</v>
       </c>
       <c r="C27">
-        <v>0.15434966561468269</v>
+        <v>0.1551369551031071</v>
       </c>
       <c r="D27">
-        <v>0.30109655491343812</v>
+        <v>0.2950946173986136</v>
       </c>
       <c r="E27">
-        <v>0.24778383896259071</v>
+        <v>0.2508339865950227</v>
       </c>
       <c r="F27">
-        <v>0.4021185009814443</v>
+        <v>0.3976994984763505</v>
       </c>
       <c r="G27">
-        <v>0.48972929254030989</v>
+        <v>0.4801255719233001</v>
       </c>
       <c r="H27">
-        <v>0.48811465308931412</v>
+        <v>0.4789997619543704</v>
       </c>
       <c r="I27">
-        <v>0.60447113513750717</v>
+        <v>0.5927997049151338</v>
       </c>
       <c r="J27">
-        <v>0.71985841886899382</v>
+        <v>0.699536214655625</v>
       </c>
       <c r="K27">
-        <v>0.79876383827549158</v>
+        <v>0.7814298454580489</v>
       </c>
       <c r="L27">
-        <v>0.91415825773814641</v>
+        <v>0.8865404659905558</v>
       </c>
       <c r="M27">
-        <v>1.0169445331102971</v>
+        <v>1.001558242555011</v>
       </c>
       <c r="N27">
-        <v>0.93398874519545849</v>
+        <v>0.9235305136833122</v>
       </c>
       <c r="O27">
-        <v>1.0262009314349581</v>
+        <v>1.018379213161983</v>
       </c>
       <c r="P27">
-        <v>1.067967105924186</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>42</v>
+        <v>1.066093485894003</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_msc_</t>
+        </is>
       </c>
       <c r="B28">
-        <v>2.6142364275411941E-2</v>
+        <v>0.02419811460020116</v>
       </c>
       <c r="C28">
-        <v>4.1024402082803217E-2</v>
+        <v>0.03874917519096599</v>
       </c>
       <c r="D28">
-        <v>5.2336277846597452E-2</v>
+        <v>0.05054808877292316</v>
       </c>
       <c r="E28">
-        <v>5.8186512472961797E-2</v>
+        <v>0.05465657739608876</v>
       </c>
       <c r="F28">
-        <v>7.5772394901790108E-2</v>
+        <v>0.07104628719727846</v>
       </c>
       <c r="G28">
-        <v>8.2230447175006827E-2</v>
+        <v>0.07871161683785055</v>
       </c>
       <c r="H28">
-        <v>9.7005706348621601E-2</v>
+        <v>0.09530580085734419</v>
       </c>
       <c r="I28">
-        <v>0.12752341176818999</v>
+        <v>0.1259326231138911</v>
       </c>
       <c r="J28">
-        <v>0.17512776718878259</v>
+        <v>0.1707190910815088</v>
       </c>
       <c r="K28">
-        <v>0.24378920275327179</v>
+        <v>0.2347452762926598</v>
       </c>
       <c r="L28">
-        <v>0.29628255804185871</v>
+        <v>0.288136488446498</v>
       </c>
       <c r="M28">
-        <v>0.37399406761072779</v>
+        <v>0.3633661347205085</v>
       </c>
       <c r="N28">
-        <v>0.45067053585713102</v>
+        <v>0.4405836265817638</v>
       </c>
       <c r="O28">
-        <v>0.54088092825104828</v>
+        <v>0.5310917632196488</v>
       </c>
       <c r="P28">
-        <v>0.64661483144499798</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>43</v>
+        <v>0.633931090483314</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_</t>
+        </is>
       </c>
       <c r="B29">
-        <v>2.5661831840711798E-2</v>
+        <v>0.02911976786186676</v>
       </c>
       <c r="C29">
-        <v>4.1133755683108619E-2</v>
+        <v>0.04308994485595652</v>
       </c>
       <c r="D29">
-        <v>5.5879432106893057E-2</v>
+        <v>0.05682926094832241</v>
       </c>
       <c r="E29">
-        <v>5.4875184938228183E-2</v>
+        <v>0.05862198916775474</v>
       </c>
       <c r="F29">
-        <v>6.7054762955570224E-2</v>
+        <v>0.06840202941326334</v>
       </c>
       <c r="G29">
-        <v>6.7129860471248359E-2</v>
+        <v>0.06940327448405204</v>
       </c>
       <c r="H29">
-        <v>7.6955834613199769E-2</v>
+        <v>0.07731716842614444</v>
       </c>
       <c r="I29">
-        <v>0.14163895640496341</v>
+        <v>0.1471194075381591</v>
       </c>
       <c r="J29">
-        <v>0.1468008974527083</v>
+        <v>0.1540609321222446</v>
       </c>
       <c r="K29">
-        <v>0.1761746712164777</v>
+        <v>0.1811043103256175</v>
       </c>
       <c r="L29">
-        <v>0.2306024447940109</v>
+        <v>0.2357684345912846</v>
       </c>
       <c r="M29">
-        <v>0.27422450868091791</v>
+        <v>0.2787746039449787</v>
       </c>
       <c r="N29">
-        <v>0.34983324431516488</v>
+        <v>0.3542977661509743</v>
       </c>
       <c r="O29">
-        <v>0.40019077954165749</v>
+        <v>0.404090564075623</v>
       </c>
       <c r="P29">
-        <v>0.52312485565543843</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>44</v>
+        <v>0.5275327294696023</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_</t>
+        </is>
       </c>
       <c r="B30">
-        <v>2.758963560024463E-2</v>
+        <v>0.02790687255925328</v>
       </c>
       <c r="C30">
-        <v>4.4430634356051317E-2</v>
+        <v>0.04309963867034317</v>
       </c>
       <c r="D30">
-        <v>6.9990340506305149E-2</v>
+        <v>0.06584151960420193</v>
       </c>
       <c r="E30">
-        <v>6.0582428383399889E-2</v>
+        <v>0.05690621642872562</v>
       </c>
       <c r="F30">
-        <v>8.1993253221517848E-2</v>
+        <v>0.07456041295527593</v>
       </c>
       <c r="G30">
-        <v>8.7412976045276536E-2</v>
+        <v>0.08024555820269064</v>
       </c>
       <c r="H30">
-        <v>9.7274482871751777E-2</v>
+        <v>0.09121027323173792</v>
       </c>
       <c r="I30">
-        <v>0.1252704054510885</v>
+        <v>0.1181303040587351</v>
       </c>
       <c r="J30">
-        <v>0.21052889282018919</v>
+        <v>0.2012125532963598</v>
       </c>
       <c r="K30">
-        <v>0.24785413097995129</v>
+        <v>0.2372506593022026</v>
       </c>
       <c r="L30">
-        <v>0.31477740349032751</v>
+        <v>0.3083795658253702</v>
       </c>
       <c r="M30">
-        <v>0.36801124517627309</v>
+        <v>0.3582205181553126</v>
       </c>
       <c r="N30">
-        <v>0.43302351787986593</v>
+        <v>0.4264661992245584</v>
       </c>
       <c r="O30">
-        <v>0.52730152276061504</v>
+        <v>0.5229164651107947</v>
       </c>
       <c r="P30">
-        <v>0.60519126883161722</v>
-      </c>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>45</v>
+        <v>0.5985345919458491</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B31">
-        <v>2.407197678789819E-2</v>
+        <v>0.02731403279390598</v>
       </c>
       <c r="C31">
-        <v>4.0567689879035702E-2</v>
+        <v>0.04200372167207533</v>
       </c>
       <c r="D31">
-        <v>6.4072876090574105E-2</v>
+        <v>0.06481457411673608</v>
       </c>
       <c r="E31">
-        <v>5.5517301776122692E-2</v>
+        <v>0.05517950044864461</v>
       </c>
       <c r="F31">
-        <v>7.510435226158807E-2</v>
+        <v>0.07477656241776665</v>
       </c>
       <c r="G31">
-        <v>7.8995375046146732E-2</v>
+        <v>0.07654903437114591</v>
       </c>
       <c r="H31">
-        <v>8.6228849001604657E-2</v>
+        <v>0.08354210092316516</v>
       </c>
       <c r="I31">
-        <v>0.1035532483584829</v>
+        <v>0.1000809448099598</v>
       </c>
       <c r="J31">
-        <v>0.15413393260717359</v>
+        <v>0.1470982648923325</v>
       </c>
       <c r="K31">
-        <v>0.1938548500503344</v>
+        <v>0.1833264671486865</v>
       </c>
       <c r="L31">
-        <v>0.2458744755689416</v>
+        <v>0.2303312546859776</v>
       </c>
       <c r="M31">
-        <v>0.30858824304670068</v>
+        <v>0.2895448073381215</v>
       </c>
       <c r="N31">
-        <v>0.33166324588492158</v>
+        <v>0.3116597451163819</v>
       </c>
       <c r="O31">
-        <v>0.34083513429990941</v>
+        <v>0.3233654297474245</v>
       </c>
       <c r="P31">
-        <v>0.41350867359861598</v>
-      </c>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>46</v>
+        <v>0.3888415404569771</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,21)_</t>
+        </is>
       </c>
       <c r="B32">
-        <v>2.6274253411779691E-2</v>
+        <v>0.02782457371541258</v>
       </c>
       <c r="C32">
-        <v>4.0027455501830289E-2</v>
+        <v>0.0419969461340931</v>
       </c>
       <c r="D32">
-        <v>5.6521208040313797E-2</v>
+        <v>0.05552535794414881</v>
       </c>
       <c r="E32">
-        <v>5.6886989167443502E-2</v>
+        <v>0.05623439740258696</v>
       </c>
       <c r="F32">
-        <v>6.6555017486676471E-2</v>
+        <v>0.06729478443585635</v>
       </c>
       <c r="G32">
-        <v>6.6078864603249854E-2</v>
+        <v>0.06629928013400688</v>
       </c>
       <c r="H32">
-        <v>7.2112639663578837E-2</v>
+        <v>0.07444087804325916</v>
       </c>
       <c r="I32">
-        <v>0.1170005418259614</v>
+        <v>0.1199910658375228</v>
       </c>
       <c r="J32">
-        <v>0.11926043759757279</v>
+        <v>0.1189935019666026</v>
       </c>
       <c r="K32">
-        <v>0.12456453852298099</v>
+        <v>0.1241797106560119</v>
       </c>
       <c r="L32">
-        <v>0.15344908070502589</v>
+        <v>0.1535926930238583</v>
       </c>
       <c r="M32">
-        <v>0.21630219863693151</v>
+        <v>0.2143145445172301</v>
       </c>
       <c r="N32">
-        <v>0.23913307579435431</v>
+        <v>0.2413024513530871</v>
       </c>
       <c r="O32">
-        <v>0.26084276705670978</v>
+        <v>0.2631233178038774</v>
       </c>
       <c r="P32">
-        <v>0.31001671680226378</v>
-      </c>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>47</v>
+        <v>0.3120360426513248</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,25)_</t>
+        </is>
       </c>
       <c r="B33">
-        <v>2.9976997973477418E-2</v>
+        <v>0.0266099805989326</v>
       </c>
       <c r="C33">
-        <v>4.4311946058140483E-2</v>
+        <v>0.04167573464929941</v>
       </c>
       <c r="D33">
-        <v>5.8245931505282227E-2</v>
+        <v>0.05440012151873386</v>
       </c>
       <c r="E33">
-        <v>5.7983337683728209E-2</v>
+        <v>0.05399539651924079</v>
       </c>
       <c r="F33">
-        <v>6.6314421077186325E-2</v>
+        <v>0.06549627677866299</v>
       </c>
       <c r="G33">
-        <v>6.623808178819568E-2</v>
+        <v>0.06553988631250696</v>
       </c>
       <c r="H33">
-        <v>7.3468990143307322E-2</v>
+        <v>0.07121324492046399</v>
       </c>
       <c r="I33">
-        <v>0.1198453625400332</v>
+        <v>0.1135858728243196</v>
       </c>
       <c r="J33">
-        <v>0.1211945937442427</v>
+        <v>0.1132410638480256</v>
       </c>
       <c r="K33">
-        <v>0.12696825528778971</v>
+        <v>0.1164255630642757</v>
       </c>
       <c r="L33">
-        <v>0.15348194383896399</v>
+        <v>0.14349109657345</v>
       </c>
       <c r="M33">
-        <v>0.21295066703511689</v>
+        <v>0.1974072903807988</v>
       </c>
       <c r="N33">
-        <v>0.2444325168303442</v>
+        <v>0.2246695058191379</v>
       </c>
       <c r="O33">
-        <v>0.26680942882014308</v>
+        <v>0.2449621878686425</v>
       </c>
       <c r="P33">
-        <v>0.30408828247092118</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>48</v>
+        <v>0.28017818874537</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,27)_</t>
+        </is>
       </c>
       <c r="B34">
-        <v>2.512801451417546E-2</v>
+        <v>0.0253477351797341</v>
       </c>
       <c r="C34">
-        <v>3.9099544462299352E-2</v>
+        <v>0.04064638490916772</v>
       </c>
       <c r="D34">
-        <v>5.2615364858810458E-2</v>
+        <v>0.05529237445211344</v>
       </c>
       <c r="E34">
-        <v>5.3852072372280957E-2</v>
+        <v>0.05397707625026882</v>
       </c>
       <c r="F34">
-        <v>6.3894421902480625E-2</v>
-      </c>
-      <c r="G34" s="2">
-        <v>6.2569114109996771E-2</v>
+        <v>0.0636851236331093</v>
+      </c>
+      <c r="G34">
+        <v>0.06341635260706313</v>
       </c>
       <c r="H34">
-        <v>6.8052855297647596E-2</v>
+        <v>0.07024296170532429</v>
       </c>
       <c r="I34">
-        <v>0.1130488533419417</v>
+        <v>0.1120856901749948</v>
       </c>
       <c r="J34">
-        <v>0.1157635805846379</v>
+        <v>0.1119153203622284</v>
       </c>
       <c r="K34">
-        <v>0.11750455442882229</v>
+        <v>0.1158373423872159</v>
       </c>
       <c r="L34">
-        <v>0.14241818609621171</v>
+        <v>0.1414701862374984</v>
       </c>
       <c r="M34">
-        <v>0.19392090301704021</v>
+        <v>0.1902474066979764</v>
       </c>
       <c r="N34">
-        <v>0.2230270782773667</v>
+        <v>0.2205378726565311</v>
       </c>
       <c r="O34">
-        <v>0.24294101248471281</v>
+        <v>0.2398244488050976</v>
       </c>
       <c r="P34">
-        <v>0.26823558874936743</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>49</v>
+        <v>0.2714538919106422</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,31)_</t>
+        </is>
       </c>
       <c r="B35">
-        <v>2.7924851702986642E-2</v>
+        <v>0.02903239182969874</v>
       </c>
       <c r="C35">
-        <v>4.1847898997635753E-2</v>
+        <v>0.04346613479262584</v>
       </c>
       <c r="D35">
-        <v>5.5580140207767033E-2</v>
+        <v>0.05615203996506546</v>
       </c>
       <c r="E35">
-        <v>5.4192614753399981E-2</v>
+        <v>0.05593516050042679</v>
       </c>
       <c r="F35">
-        <v>6.3176577054532723E-2</v>
+        <v>0.06522806382221902</v>
       </c>
       <c r="G35">
-        <v>6.3579687191670398E-2</v>
+        <v>0.06266895416420781</v>
       </c>
       <c r="H35">
-        <v>6.8298957917332315E-2</v>
+        <v>0.06900664685649016</v>
       </c>
       <c r="I35">
-        <v>0.1140613888292195</v>
+        <v>0.1116016166042655</v>
       </c>
       <c r="J35">
-        <v>0.1165862979016979</v>
+        <v>0.1115552335179161</v>
       </c>
       <c r="K35">
-        <v>0.11715215551645709</v>
+        <v>0.1145636564214557</v>
       </c>
       <c r="L35">
-        <v>0.13974734746275269</v>
+        <v>0.1388787925848785</v>
       </c>
       <c r="M35">
-        <v>0.18275500825812979</v>
+        <v>0.1860633131889536</v>
       </c>
       <c r="N35">
-        <v>0.21415483906631569</v>
+        <v>0.2175681920576297</v>
       </c>
       <c r="O35">
-        <v>0.2359307996104382</v>
+        <v>0.2417851354215649</v>
       </c>
       <c r="P35">
-        <v>0.2484359491324496</v>
-      </c>
-    </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>50</v>
+        <v>0.2544995242470547</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
+        </is>
       </c>
       <c r="B36">
-        <v>2.815359783619242E-2</v>
+        <v>0.02628792227927612</v>
       </c>
       <c r="C36">
-        <v>4.1587176405809001E-2</v>
+        <v>0.03966455786513523</v>
       </c>
       <c r="D36">
-        <v>5.4908191727837008E-2</v>
+        <v>0.05380880740643301</v>
       </c>
       <c r="E36">
-        <v>5.5110194522254852E-2</v>
+        <v>0.05281096078529424</v>
       </c>
       <c r="F36">
-        <v>6.5871357099776207E-2</v>
+        <v>0.06269805810997353</v>
       </c>
       <c r="G36">
-        <v>6.556001800916178E-2</v>
+        <v>0.0629437101030883</v>
       </c>
       <c r="H36">
-        <v>7.3241906130985246E-2</v>
+        <v>0.06800495330924639</v>
       </c>
       <c r="I36">
-        <v>0.12110856269245771</v>
+        <v>0.112453514463432</v>
       </c>
       <c r="J36">
-        <v>0.121538732447972</v>
+        <v>0.1158504314386174</v>
       </c>
       <c r="K36">
-        <v>0.1275747905559548</v>
+        <v>0.123309936208694</v>
       </c>
       <c r="L36">
-        <v>0.1699760857531106</v>
+        <v>0.1646393275049938</v>
       </c>
       <c r="M36">
-        <v>0.22797584760365139</v>
+        <v>0.221963498734347</v>
       </c>
       <c r="N36">
-        <v>0.24962091465913949</v>
+        <v>0.2400142249169225</v>
       </c>
       <c r="O36">
-        <v>0.27018770746487442</v>
+        <v>0.2607591600935986</v>
       </c>
       <c r="P36">
-        <v>0.34553655340399198</v>
-      </c>
-    </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>51</v>
+        <v>0.3369868810914933</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,17)_</t>
+        </is>
       </c>
       <c r="B37">
-        <v>2.8616522540874101E-2</v>
+        <v>0.02905604336530332</v>
       </c>
       <c r="C37">
-        <v>4.2590883304464811E-2</v>
+        <v>0.04384565490702763</v>
       </c>
       <c r="D37">
-        <v>5.5507623406821471E-2</v>
+        <v>0.05689603116537523</v>
       </c>
       <c r="E37">
-        <v>5.5659268144310443E-2</v>
+        <v>0.05552891641799174</v>
       </c>
       <c r="F37">
-        <v>6.5105721059545374E-2</v>
+        <v>0.06577940163842255</v>
       </c>
       <c r="G37">
-        <v>6.6506873977689063E-2</v>
+        <v>0.06502382980586607</v>
       </c>
       <c r="H37">
-        <v>7.2594448316156357E-2</v>
+        <v>0.07108769553398753</v>
       </c>
       <c r="I37">
-        <v>0.11850601863058791</v>
+        <v>0.1166470017047363</v>
       </c>
       <c r="J37">
-        <v>0.1181030455211214</v>
+        <v>0.1185477603620819</v>
       </c>
       <c r="K37">
-        <v>0.12574539029879911</v>
+        <v>0.1245349806499052</v>
       </c>
       <c r="L37">
-        <v>0.1646190100952615</v>
+        <v>0.163321142607449</v>
       </c>
       <c r="M37">
-        <v>0.22700874618951181</v>
+        <v>0.2258309762870601</v>
       </c>
       <c r="N37">
-        <v>0.25045235793255061</v>
+        <v>0.24776015214932</v>
       </c>
       <c r="O37">
-        <v>0.27099568383204092</v>
+        <v>0.2669383976898932</v>
       </c>
       <c r="P37">
-        <v>0.33658866896538758</v>
-      </c>
-    </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>52</v>
+        <v>0.3355575116351802</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,19)_</t>
+        </is>
       </c>
       <c r="B38">
-        <v>2.7181395724907961E-2</v>
+        <v>0.02763914563790659</v>
       </c>
       <c r="C38">
-        <v>4.1798804221880197E-2</v>
+        <v>0.04264484167234572</v>
       </c>
       <c r="D38">
-        <v>5.6548911093975751E-2</v>
+        <v>0.05878006423429627</v>
       </c>
       <c r="E38">
-        <v>5.5766818459887728E-2</v>
+        <v>0.0570365748076086</v>
       </c>
       <c r="F38">
-        <v>6.5670610827739062E-2</v>
+        <v>0.06605268278655474</v>
       </c>
       <c r="G38">
-        <v>6.5206926945136079E-2</v>
+        <v>0.06693229477655727</v>
       </c>
       <c r="H38">
-        <v>7.223736257290847E-2</v>
+        <v>0.07606014520842763</v>
       </c>
       <c r="I38">
-        <v>0.119623237617455</v>
+        <v>0.1210306264427237</v>
       </c>
       <c r="J38">
-        <v>0.1182325264651528</v>
+        <v>0.1198074568311024</v>
       </c>
       <c r="K38">
-        <v>0.1237108181952296</v>
+        <v>0.1260369267471414</v>
       </c>
       <c r="L38">
-        <v>0.16134269520976929</v>
+        <v>0.1600354803481153</v>
       </c>
       <c r="M38">
-        <v>0.22661623972569511</v>
+        <v>0.2243452572562812</v>
       </c>
       <c r="N38">
-        <v>0.25139847690484629</v>
+        <v>0.2490923802193709</v>
       </c>
       <c r="O38">
-        <v>0.27092372069567361</v>
+        <v>0.26880251663857</v>
       </c>
       <c r="P38">
-        <v>0.32499715427415049</v>
-      </c>
-    </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>53</v>
+        <v>0.3259008496205419</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B39">
-        <v>2.8900437750458811E-2</v>
+        <v>0.02921918249039279</v>
       </c>
       <c r="C39">
-        <v>4.3219843047890283E-2</v>
+        <v>0.04359883719705027</v>
       </c>
       <c r="D39">
-        <v>5.7112263174944E-2</v>
+        <v>0.05812038669594544</v>
       </c>
       <c r="E39">
-        <v>5.607877822596774E-2</v>
+        <v>0.05673759117386634</v>
       </c>
       <c r="F39">
-        <v>6.6174502647181166E-2</v>
+        <v>0.06590024020476049</v>
       </c>
       <c r="G39">
-        <v>6.5767909798459367E-2</v>
+        <v>0.06585421692437066</v>
       </c>
       <c r="H39">
-        <v>7.1587255159210605E-2</v>
+        <v>0.07211651268987029</v>
       </c>
       <c r="I39">
-        <v>0.117826096473671</v>
+        <v>0.1150080463000205</v>
       </c>
       <c r="J39">
-        <v>0.1177097968482301</v>
+        <v>0.1155229846419782</v>
       </c>
       <c r="K39">
-        <v>0.12609999124783039</v>
+        <v>0.1198258299827544</v>
       </c>
       <c r="L39">
-        <v>0.15889370896252611</v>
+        <v>0.1565878405499468</v>
       </c>
       <c r="M39">
-        <v>0.22369531755570049</v>
+        <v>0.218986989321039</v>
       </c>
       <c r="N39">
-        <v>0.25015098867012209</v>
+        <v>0.2474176998056722</v>
       </c>
       <c r="O39">
-        <v>0.26556308848995003</v>
+        <v>0.2664570665414451</v>
       </c>
       <c r="P39">
-        <v>0.31221563487094589</v>
-      </c>
-    </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>54</v>
+        <v>0.3246828665444654</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
+        </is>
       </c>
       <c r="B40">
-        <v>3.067000745187776E-2</v>
+        <v>0.02710787645125923</v>
       </c>
       <c r="C40">
-        <v>4.4172145031392003E-2</v>
+        <v>0.04093450555344857</v>
       </c>
       <c r="D40">
-        <v>5.78002150140422E-2</v>
+        <v>0.05455861789129235</v>
       </c>
       <c r="E40">
-        <v>5.7033063284867347E-2</v>
+        <v>0.05468845728792548</v>
       </c>
       <c r="F40">
-        <v>6.4610065444081877E-2</v>
+        <v>0.06592589595026188</v>
       </c>
       <c r="G40">
-        <v>6.5026350696428259E-2</v>
+        <v>0.06242169979493661</v>
       </c>
       <c r="H40">
-        <v>6.9543483736913547E-2</v>
+        <v>0.06952365122217385</v>
       </c>
       <c r="I40">
-        <v>0.11383795166087141</v>
+        <v>0.1118350668976633</v>
       </c>
       <c r="J40">
-        <v>0.1146618186626871</v>
+        <v>0.1139835540074299</v>
       </c>
       <c r="K40">
-        <v>0.1175641371724027</v>
+        <v>0.1158718924926467</v>
       </c>
       <c r="L40">
-        <v>0.14361951423229111</v>
+        <v>0.1402335535675159</v>
       </c>
       <c r="M40">
-        <v>0.189094956613893</v>
+        <v>0.1861448826539139</v>
       </c>
       <c r="N40">
-        <v>0.21972894617910119</v>
+        <v>0.2176489840436018</v>
       </c>
       <c r="O40">
-        <v>0.2419077325159931</v>
+        <v>0.2387119273735161</v>
       </c>
       <c r="P40">
-        <v>0.26153385214648978</v>
-      </c>
-    </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>55</v>
+        <v>0.2572743094627755</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B41">
-        <v>3.0155501251459271E-2</v>
+        <v>0.02920307087371043</v>
       </c>
       <c r="C41">
-        <v>0.11836364724763521</v>
+        <v>0.1226741034697751</v>
       </c>
       <c r="D41">
-        <v>7.54929805284833E-2</v>
+        <v>0.07654632644315662</v>
       </c>
       <c r="E41">
-        <v>8.9168101431702507E-2</v>
+        <v>0.08993389173588318</v>
       </c>
       <c r="F41">
-        <v>0.15910788379275809</v>
+        <v>0.1592131701979551</v>
       </c>
       <c r="G41">
-        <v>0.19226880441406069</v>
+        <v>0.1919084043113735</v>
       </c>
       <c r="H41">
-        <v>0.19743162695209099</v>
+        <v>0.1950145089149274</v>
       </c>
       <c r="I41">
-        <v>0.22910103113566441</v>
+        <v>0.2255075596444307</v>
       </c>
       <c r="J41">
-        <v>0.2958751524090435</v>
+        <v>0.2921711318424492</v>
       </c>
       <c r="K41">
-        <v>0.35785595621242561</v>
+        <v>0.3564092067520778</v>
       </c>
       <c r="L41">
-        <v>0.4117422276481823</v>
+        <v>0.4072260815408846</v>
       </c>
       <c r="M41">
-        <v>0.45971203835158081</v>
+        <v>0.4526067604785843</v>
       </c>
       <c r="N41">
-        <v>0.49735445589560462</v>
+        <v>0.4887867100253367</v>
       </c>
       <c r="O41">
-        <v>0.53748882172738344</v>
+        <v>0.5284714211449755</v>
       </c>
       <c r="P41">
-        <v>0.56703793802046709</v>
-      </c>
-    </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>56</v>
+        <v>0.5539958320559889</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,25)_</t>
+        </is>
       </c>
       <c r="B42">
-        <v>2.8320856279248959E-2</v>
+        <v>0.02951425895158977</v>
       </c>
       <c r="C42">
-        <v>9.993362034567066E-2</v>
+        <v>0.1046184918847359</v>
       </c>
       <c r="D42">
-        <v>5.8573006601299271E-2</v>
+        <v>0.06165640354104096</v>
       </c>
       <c r="E42">
-        <v>6.846722121821236E-2</v>
+        <v>0.07196022491966325</v>
       </c>
       <c r="F42">
-        <v>0.10427991540111491</v>
+        <v>0.1112752331928549</v>
       </c>
       <c r="G42">
-        <v>0.15712390736382911</v>
+        <v>0.1624456611808835</v>
       </c>
       <c r="H42">
-        <v>0.1325754823322772</v>
+        <v>0.1353939295158605</v>
       </c>
       <c r="I42">
-        <v>0.16684975654837961</v>
+        <v>0.1672291425197678</v>
       </c>
       <c r="J42">
-        <v>0.21826021715680019</v>
+        <v>0.2150293422566958</v>
       </c>
       <c r="K42">
-        <v>0.25310026660432622</v>
+        <v>0.2497645986932844</v>
       </c>
       <c r="L42">
-        <v>0.27608414886128502</v>
+        <v>0.2736633260980973</v>
       </c>
       <c r="M42">
-        <v>0.33154591120291049</v>
+        <v>0.3283727440567289</v>
       </c>
       <c r="N42">
-        <v>0.38857157164737322</v>
+        <v>0.3880293426987568</v>
       </c>
       <c r="O42">
-        <v>0.46144132106950819</v>
+        <v>0.456995210419276</v>
       </c>
       <c r="P42">
-        <v>0.5250105186145364</v>
-      </c>
-    </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>57</v>
+        <v>0.5245707091667495</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
+        </is>
       </c>
       <c r="B43">
-        <v>2.7866481029913182E-2</v>
+        <v>0.02822536472010895</v>
       </c>
       <c r="C43">
-        <v>0.10047295014334109</v>
+        <v>0.1014887398648686</v>
       </c>
       <c r="D43">
-        <v>5.4793788346106147E-2</v>
+        <v>0.05970755811042416</v>
       </c>
       <c r="E43">
-        <v>6.5010705002288671E-2</v>
+        <v>0.06885233581203365</v>
       </c>
       <c r="F43">
-        <v>9.1188779924773145E-2</v>
+        <v>0.09403195258496222</v>
       </c>
       <c r="G43">
-        <v>0.13066478978147311</v>
+        <v>0.1386156954774042</v>
       </c>
       <c r="H43">
-        <v>0.1188391043377751</v>
+        <v>0.1264172281056268</v>
       </c>
       <c r="I43">
-        <v>0.1499789840011326</v>
+        <v>0.1581355303365224</v>
       </c>
       <c r="J43">
-        <v>0.19724144789690909</v>
+        <v>0.2058480259115085</v>
       </c>
       <c r="K43">
-        <v>0.2501185473443025</v>
+        <v>0.2582702875765093</v>
       </c>
       <c r="L43">
-        <v>0.28759504120897561</v>
+        <v>0.294300889646169</v>
       </c>
       <c r="M43">
-        <v>0.36258492114462798</v>
+        <v>0.3742373217967828</v>
       </c>
       <c r="N43">
-        <v>0.3998854159893207</v>
+        <v>0.4098761635622749</v>
       </c>
       <c r="O43">
-        <v>0.43391737312401207</v>
+        <v>0.4404630132405721</v>
       </c>
       <c r="P43">
-        <v>0.48046705004450152</v>
-      </c>
-    </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>58</v>
+        <v>0.4928186312615779</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(2,3,21)_</t>
+        </is>
       </c>
       <c r="B44">
-        <v>3.5391927110677401E-2</v>
+        <v>0.033464897062078</v>
       </c>
       <c r="C44">
-        <v>6.0449193909543397E-2</v>
+        <v>0.06234482230259508</v>
       </c>
       <c r="D44">
-        <v>8.6156917264805233E-2</v>
+        <v>0.09132677487113172</v>
       </c>
       <c r="E44">
-        <v>0.1039575858887332</v>
+        <v>0.1035696284572728</v>
       </c>
       <c r="F44">
-        <v>0.1351750272827533</v>
+        <v>0.129769687677024</v>
       </c>
       <c r="G44">
-        <v>0.16372439733402239</v>
+        <v>0.1568602737091465</v>
       </c>
       <c r="H44">
-        <v>0.2238626992927758</v>
+        <v>0.2156731550664198</v>
       </c>
       <c r="I44">
-        <v>0.25444203704909429</v>
+        <v>0.2468554757579094</v>
       </c>
       <c r="J44">
-        <v>0.29520869834120289</v>
+        <v>0.2878454142660121</v>
       </c>
       <c r="K44">
-        <v>0.35825456896285179</v>
+        <v>0.3524921671894462</v>
       </c>
       <c r="L44">
-        <v>0.44867406317665182</v>
+        <v>0.4395500867850628</v>
       </c>
       <c r="M44">
-        <v>0.54350007256366861</v>
+        <v>0.5360266788366168</v>
       </c>
       <c r="N44">
-        <v>0.60876076375412391</v>
+        <v>0.6061323963957561</v>
       </c>
       <c r="O44">
-        <v>0.68645928037990755</v>
+        <v>0.6896520107462731</v>
       </c>
       <c r="P44">
-        <v>0.76275216863105966</v>
-      </c>
-    </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>59</v>
+        <v>0.7704583571308777</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>adj_snv_sder_c(1,3,5)_</t>
+        </is>
       </c>
       <c r="B45">
-        <v>4.2093474338625647E-2</v>
+        <v>0.04071891039006986</v>
       </c>
       <c r="C45">
-        <v>6.6045136397546389E-2</v>
+        <v>0.06452128123790268</v>
       </c>
       <c r="D45">
-        <v>0.15785119803066361</v>
+        <v>0.1560498354825868</v>
       </c>
       <c r="E45">
-        <v>0.26326008306536319</v>
+        <v>0.2586346077308677</v>
       </c>
       <c r="F45">
-        <v>0.39364333878956992</v>
+        <v>0.3830735354241279</v>
       </c>
       <c r="G45">
-        <v>0.43550086755197293</v>
+        <v>0.426594163825658</v>
       </c>
       <c r="H45">
-        <v>0.41315407313506602</v>
+        <v>0.4051123975643586</v>
       </c>
       <c r="I45">
-        <v>0.41418084578844883</v>
+        <v>0.4115288157860641</v>
       </c>
       <c r="J45">
-        <v>0.44006251409318131</v>
+        <v>0.4357233176960568</v>
       </c>
       <c r="K45">
-        <v>0.51403137516543462</v>
+        <v>0.5074897128241274</v>
       </c>
       <c r="L45">
-        <v>0.62352389338626857</v>
+        <v>0.6159945055432314</v>
       </c>
       <c r="M45">
-        <v>0.68731916722099151</v>
+        <v>0.6844522823647415</v>
       </c>
       <c r="N45">
-        <v>0.74512822510836241</v>
+        <v>0.742923940058603</v>
       </c>
       <c r="O45">
-        <v>0.80479541340763838</v>
+        <v>0.8025762973681543</v>
       </c>
       <c r="P45">
-        <v>0.82305155568575672</v>
-      </c>
-    </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>60</v>
+        <v>0.8146618728672678</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>adj_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B46">
-        <v>4.7202566311814687E-2</v>
+        <v>0.04456598188450372</v>
       </c>
       <c r="C46">
-        <v>4.8163559541547503E-2</v>
+        <v>0.04781881448075287</v>
       </c>
       <c r="D46">
-        <v>0.1244200104517052</v>
+        <v>0.1259879787446392</v>
       </c>
       <c r="E46">
-        <v>0.16288562898714201</v>
+        <v>0.1657191073469815</v>
       </c>
       <c r="F46">
-        <v>0.23872694561563329</v>
+        <v>0.2355009623172741</v>
       </c>
       <c r="G46">
-        <v>0.23473097016808489</v>
+        <v>0.2339144678488333</v>
       </c>
       <c r="H46">
-        <v>0.2452372129534115</v>
+        <v>0.2413250037854349</v>
       </c>
       <c r="I46">
-        <v>0.32285059999526572</v>
+        <v>0.3169816170560619</v>
       </c>
       <c r="J46">
-        <v>0.38360524590991502</v>
+        <v>0.3740453460718787</v>
       </c>
       <c r="K46">
-        <v>0.47375269743230608</v>
+        <v>0.463392372112455</v>
       </c>
       <c r="L46">
-        <v>0.51421321051194202</v>
+        <v>0.5032268295289783</v>
       </c>
       <c r="M46">
-        <v>0.55349999260967697</v>
+        <v>0.5374521297236149</v>
       </c>
       <c r="N46">
-        <v>0.58606785886554424</v>
+        <v>0.5674041282227686</v>
       </c>
       <c r="O46">
-        <v>0.62046745248635482</v>
+        <v>0.6037161752601597</v>
       </c>
       <c r="P46">
-        <v>0.66181110638631624</v>
-      </c>
-    </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>61</v>
+        <v>0.6383513012025772</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>snv_sder_c(1,3,9)_red_c(10,10,1)_</t>
+        </is>
       </c>
       <c r="B47">
-        <v>3.2410514652598033E-2</v>
+        <v>0.03199320361235436</v>
       </c>
       <c r="C47">
-        <v>0.1006547165382015</v>
+        <v>0.1003839728586005</v>
       </c>
       <c r="D47">
-        <v>0.1428140847020184</v>
+        <v>0.1421556861827729</v>
       </c>
       <c r="E47">
-        <v>0.2165753618329388</v>
+        <v>0.2183999474424864</v>
       </c>
       <c r="F47">
-        <v>0.35399426019296409</v>
+        <v>0.3611905691083123</v>
       </c>
       <c r="G47">
-        <v>0.37805480434273719</v>
+        <v>0.381533257709403</v>
       </c>
       <c r="H47">
-        <v>0.31133475915251829</v>
+        <v>0.314539981931479</v>
       </c>
       <c r="I47">
-        <v>0.31611207579257949</v>
+        <v>0.3217404381422787</v>
       </c>
       <c r="J47">
-        <v>0.36304975044033427</v>
+        <v>0.3735555132051305</v>
       </c>
       <c r="K47">
-        <v>0.45517396983489822</v>
+        <v>0.4696856945905256</v>
       </c>
       <c r="L47">
-        <v>0.50614423012589393</v>
+        <v>0.5150438377524462</v>
       </c>
       <c r="M47">
-        <v>0.53691512248843254</v>
+        <v>0.5459837240219951</v>
       </c>
       <c r="N47">
-        <v>0.55383739855526903</v>
+        <v>0.5576657089306283</v>
       </c>
       <c r="O47">
-        <v>0.55877939136287313</v>
+        <v>0.5607985253010529</v>
       </c>
       <c r="P47">
-        <v>0.56945206195778564</v>
+        <v>0.5702751941914947</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:P33 B35:P47 B34:F34 H34:P34">
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="lessThan">
-      <formula>0.21</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="greaterThan">
-      <formula>0.21</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/ROSA_vitaSPEC/Results/test_pretraitements/trans.beta.carotenes/Resultats_trans.beta.carotenes_moy_diff.xlsx
+++ b/ROSA_vitaSPEC/Results/test_pretraitements/trans.beta.carotenes/Resultats_trans.beta.carotenes_moy_diff.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P47"/>
+  <dimension ref="A1:P43"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -443,49 +443,49 @@
         </is>
       </c>
       <c r="B2">
-        <v>0.03925080979722251</v>
+        <v>0.03995056415622034</v>
       </c>
       <c r="C2">
-        <v>0.05951201704284392</v>
+        <v>0.05930584437999753</v>
       </c>
       <c r="D2">
-        <v>0.08419574319673762</v>
+        <v>0.08138728229998127</v>
       </c>
       <c r="E2">
-        <v>0.08482486876791973</v>
+        <v>0.08243246760500644</v>
       </c>
       <c r="F2">
-        <v>0.1303373343065161</v>
+        <v>0.1267493041016561</v>
       </c>
       <c r="G2">
-        <v>0.134694465623883</v>
+        <v>0.1330882074496562</v>
       </c>
       <c r="H2">
-        <v>0.1627288312272666</v>
+        <v>0.1622076806622207</v>
       </c>
       <c r="I2">
-        <v>0.1725318156769989</v>
+        <v>0.1687876605296922</v>
       </c>
       <c r="J2">
-        <v>0.1874276260016305</v>
+        <v>0.1828136033328468</v>
       </c>
       <c r="K2">
-        <v>0.2000451461052175</v>
+        <v>0.1976938834813543</v>
       </c>
       <c r="L2">
-        <v>0.2626506034022283</v>
+        <v>0.265587782328714</v>
       </c>
       <c r="M2">
-        <v>0.3173969996726505</v>
+        <v>0.3239169152485389</v>
       </c>
       <c r="N2">
-        <v>0.3827254220485842</v>
+        <v>0.3959493983520482</v>
       </c>
       <c r="O2">
-        <v>0.4719946906815988</v>
+        <v>0.4925477855814624</v>
       </c>
       <c r="P2">
-        <v>0.4524490853042606</v>
+        <v>0.4723781554077854</v>
       </c>
     </row>
     <row r="3">
@@ -495,49 +495,49 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.04294674602846288</v>
+        <v>0.04372368236782909</v>
       </c>
       <c r="C3">
-        <v>0.04205930974970762</v>
+        <v>0.04414154549101112</v>
       </c>
       <c r="D3">
-        <v>0.08483002268621315</v>
+        <v>0.08797615398483516</v>
       </c>
       <c r="E3">
-        <v>0.1144025217580288</v>
+        <v>0.1202302935095891</v>
       </c>
       <c r="F3">
-        <v>0.1517597196648307</v>
+        <v>0.1650337134936441</v>
       </c>
       <c r="G3">
-        <v>0.1769747533443988</v>
+        <v>0.1916684988036639</v>
       </c>
       <c r="H3">
-        <v>0.2341622105284624</v>
+        <v>0.2539664529227355</v>
       </c>
       <c r="I3">
-        <v>0.2704048221196284</v>
+        <v>0.2868273021616342</v>
       </c>
       <c r="J3">
-        <v>0.2977968909713019</v>
+        <v>0.3145718735230105</v>
       </c>
       <c r="K3">
-        <v>0.3330174386050105</v>
+        <v>0.3440384969474297</v>
       </c>
       <c r="L3">
-        <v>0.3870813710755396</v>
+        <v>0.4000272203809025</v>
       </c>
       <c r="M3">
-        <v>0.4859072875142739</v>
+        <v>0.5057279729317865</v>
       </c>
       <c r="N3">
-        <v>0.5996419809989589</v>
+        <v>0.6150927181839476</v>
       </c>
       <c r="O3">
-        <v>0.6657835068568395</v>
+        <v>0.6787803883589297</v>
       </c>
       <c r="P3">
-        <v>0.7444542645095242</v>
+        <v>0.7484842887159695</v>
       </c>
     </row>
     <row r="4">
@@ -547,49 +547,49 @@
         </is>
       </c>
       <c r="B4">
-        <v>0.03236347096039155</v>
+        <v>0.03677386168060037</v>
       </c>
       <c r="C4">
-        <v>0.04856172701455214</v>
+        <v>0.05302348994183026</v>
       </c>
       <c r="D4">
-        <v>0.06284267916970332</v>
+        <v>0.06828763193355264</v>
       </c>
       <c r="E4">
-        <v>0.1054688130568818</v>
+        <v>0.1124016162495784</v>
       </c>
       <c r="F4">
-        <v>0.1390802253308723</v>
+        <v>0.1440641649245342</v>
       </c>
       <c r="G4">
-        <v>0.115856478181798</v>
+        <v>0.123571164362399</v>
       </c>
       <c r="H4">
-        <v>0.1188994823897914</v>
+        <v>0.1245943645934999</v>
       </c>
       <c r="I4">
-        <v>0.1619847565208701</v>
+        <v>0.1683357030169078</v>
       </c>
       <c r="J4">
-        <v>0.2317336885886481</v>
+        <v>0.2372374913337783</v>
       </c>
       <c r="K4">
-        <v>0.2997189932092698</v>
+        <v>0.3019051072763347</v>
       </c>
       <c r="L4">
-        <v>0.4220362974277435</v>
+        <v>0.4299448577709425</v>
       </c>
       <c r="M4">
-        <v>0.4273994821259925</v>
+        <v>0.435980546406576</v>
       </c>
       <c r="N4">
-        <v>0.416132431755197</v>
+        <v>0.4244884910529088</v>
       </c>
       <c r="O4">
-        <v>0.3997421293183803</v>
+        <v>0.4085944493669812</v>
       </c>
       <c r="P4">
-        <v>0.40640783475848</v>
+        <v>0.4123609633481956</v>
       </c>
     </row>
     <row r="5">
@@ -599,49 +599,49 @@
         </is>
       </c>
       <c r="B5">
-        <v>0.03096878236307377</v>
+        <v>0.03162999434939756</v>
       </c>
       <c r="C5">
-        <v>0.05683617715332245</v>
+        <v>0.05834474079215074</v>
       </c>
       <c r="D5">
-        <v>0.1104341840989743</v>
+        <v>0.1120567780808241</v>
       </c>
       <c r="E5">
-        <v>0.1271643288402261</v>
+        <v>0.1338676036325005</v>
       </c>
       <c r="F5">
-        <v>0.1658874103417063</v>
+        <v>0.1747157986338993</v>
       </c>
       <c r="G5">
-        <v>0.1700664147674689</v>
+        <v>0.177159938354265</v>
       </c>
       <c r="H5">
-        <v>0.1903393406595656</v>
+        <v>0.1942196612630529</v>
       </c>
       <c r="I5">
-        <v>0.2350921924304787</v>
+        <v>0.2415731502661438</v>
       </c>
       <c r="J5">
-        <v>0.2918001644699071</v>
+        <v>0.2956153871902819</v>
       </c>
       <c r="K5">
-        <v>0.352255024314862</v>
+        <v>0.3613432634864258</v>
       </c>
       <c r="L5">
-        <v>0.4167262139524756</v>
+        <v>0.427759023368177</v>
       </c>
       <c r="M5">
-        <v>0.4653680307631478</v>
+        <v>0.4687361478811808</v>
       </c>
       <c r="N5">
-        <v>0.4581514404512513</v>
+        <v>0.4604421559707335</v>
       </c>
       <c r="O5">
-        <v>0.4736135558459898</v>
+        <v>0.4677163721202152</v>
       </c>
       <c r="P5">
-        <v>0.4652971805673781</v>
+        <v>0.4629825419596328</v>
       </c>
     </row>
     <row r="6">
@@ -651,49 +651,49 @@
         </is>
       </c>
       <c r="B6">
-        <v>0.02864112477928504</v>
+        <v>0.03094816166677794</v>
       </c>
       <c r="C6">
-        <v>0.05227648530162382</v>
+        <v>0.0566319423147828</v>
       </c>
       <c r="D6">
-        <v>0.09024718345463834</v>
+        <v>0.09403535710963323</v>
       </c>
       <c r="E6">
-        <v>0.1167393749866645</v>
+        <v>0.1171829348110687</v>
       </c>
       <c r="F6">
-        <v>0.1429544020729214</v>
+        <v>0.1390596172281477</v>
       </c>
       <c r="G6">
-        <v>0.1693514613501639</v>
+        <v>0.1668035828755529</v>
       </c>
       <c r="H6">
-        <v>0.1869623886884579</v>
+        <v>0.1833239496386088</v>
       </c>
       <c r="I6">
-        <v>0.2516699058295379</v>
+        <v>0.2482607351187432</v>
       </c>
       <c r="J6">
-        <v>0.3177674861605148</v>
+        <v>0.3149441826077055</v>
       </c>
       <c r="K6">
-        <v>0.3559252363929205</v>
+        <v>0.3479308006093809</v>
       </c>
       <c r="L6">
-        <v>0.4207369130478037</v>
+        <v>0.4174807619359003</v>
       </c>
       <c r="M6">
-        <v>0.4465295558072203</v>
+        <v>0.4413314371573487</v>
       </c>
       <c r="N6">
-        <v>0.4991205150767337</v>
+        <v>0.4939284018171255</v>
       </c>
       <c r="O6">
-        <v>0.4893347691047588</v>
+        <v>0.4779592210543107</v>
       </c>
       <c r="P6">
-        <v>0.4849181558729204</v>
+        <v>0.478335860349774</v>
       </c>
     </row>
     <row r="7">
@@ -703,49 +703,49 @@
         </is>
       </c>
       <c r="B7">
-        <v>0.03621979763616201</v>
+        <v>0.03773993384070035</v>
       </c>
       <c r="C7">
-        <v>0.0512392266310821</v>
+        <v>0.05201161716581387</v>
       </c>
       <c r="D7">
-        <v>0.08256580582571582</v>
+        <v>0.08338052962761644</v>
       </c>
       <c r="E7">
-        <v>0.07007274280824727</v>
+        <v>0.06984421136224217</v>
       </c>
       <c r="F7">
-        <v>0.09288082320735946</v>
+        <v>0.09522619967962331</v>
       </c>
       <c r="G7">
-        <v>0.1031976788625062</v>
+        <v>0.1071318058501679</v>
       </c>
       <c r="H7">
-        <v>0.1320798240066867</v>
+        <v>0.138590282041265</v>
       </c>
       <c r="I7">
-        <v>0.1424265059736812</v>
+        <v>0.1499668391703309</v>
       </c>
       <c r="J7">
-        <v>0.1820734507461869</v>
+        <v>0.1894633788615714</v>
       </c>
       <c r="K7">
-        <v>0.2499953024739631</v>
+        <v>0.2652444364151516</v>
       </c>
       <c r="L7">
-        <v>0.305883865621826</v>
+        <v>0.3225292083929456</v>
       </c>
       <c r="M7">
-        <v>0.3737282719856718</v>
+        <v>0.3900284547640841</v>
       </c>
       <c r="N7">
-        <v>0.3906952022396313</v>
+        <v>0.4056124848541973</v>
       </c>
       <c r="O7">
-        <v>0.3878928704212097</v>
+        <v>0.3998537470292209</v>
       </c>
       <c r="P7">
-        <v>0.380016283883086</v>
+        <v>0.3942532549959712</v>
       </c>
     </row>
     <row r="8">
@@ -755,49 +755,49 @@
         </is>
       </c>
       <c r="B8">
-        <v>0.03583396638131192</v>
+        <v>0.03112222306261242</v>
       </c>
       <c r="C8">
-        <v>0.0509986195634235</v>
+        <v>0.04781588139832782</v>
       </c>
       <c r="D8">
-        <v>0.07603291912879651</v>
+        <v>0.07343189662071281</v>
       </c>
       <c r="E8">
-        <v>0.1002973191960008</v>
+        <v>0.09825558706679938</v>
       </c>
       <c r="F8">
-        <v>0.1102478742128374</v>
+        <v>0.1091114611519429</v>
       </c>
       <c r="G8">
-        <v>0.1557453449996075</v>
+        <v>0.158084976930146</v>
       </c>
       <c r="H8">
-        <v>0.155645753931127</v>
+        <v>0.1608127729530289</v>
       </c>
       <c r="I8">
-        <v>0.1873480091538156</v>
+        <v>0.1912653397253927</v>
       </c>
       <c r="J8">
-        <v>0.2362021480900382</v>
+        <v>0.2416415238125305</v>
       </c>
       <c r="K8">
-        <v>0.320166646409364</v>
+        <v>0.3260271146668489</v>
       </c>
       <c r="L8">
-        <v>0.4103965944896588</v>
+        <v>0.4164625604776793</v>
       </c>
       <c r="M8">
-        <v>0.4249609911047638</v>
+        <v>0.4276611760875997</v>
       </c>
       <c r="N8">
-        <v>0.4138444692159017</v>
+        <v>0.4102087842583879</v>
       </c>
       <c r="O8">
-        <v>0.3973259840454042</v>
+        <v>0.3931381503336916</v>
       </c>
       <c r="P8">
-        <v>0.4261125810277261</v>
+        <v>0.421170287165151</v>
       </c>
     </row>
     <row r="9">
@@ -807,49 +807,49 @@
         </is>
       </c>
       <c r="B9">
-        <v>0.03128545967092666</v>
+        <v>0.03666378223246769</v>
       </c>
       <c r="C9">
-        <v>0.04627491376612275</v>
+        <v>0.0534288378958146</v>
       </c>
       <c r="D9">
-        <v>0.07076795469399877</v>
+        <v>0.07762267443438031</v>
       </c>
       <c r="E9">
-        <v>0.09493577484043914</v>
+        <v>0.1009588818500422</v>
       </c>
       <c r="F9">
-        <v>0.1050932908338237</v>
+        <v>0.1101958335596578</v>
       </c>
       <c r="G9">
-        <v>0.1498888676727641</v>
+        <v>0.1534728223710931</v>
       </c>
       <c r="H9">
-        <v>0.1466783101119326</v>
+        <v>0.1510333082825303</v>
       </c>
       <c r="I9">
-        <v>0.1723948558626897</v>
+        <v>0.1733576960277086</v>
       </c>
       <c r="J9">
-        <v>0.1950591215806495</v>
+        <v>0.2001104652735453</v>
       </c>
       <c r="K9">
-        <v>0.2389724661498718</v>
+        <v>0.2445003029063681</v>
       </c>
       <c r="L9">
-        <v>0.3134832846413961</v>
+        <v>0.3235725396730977</v>
       </c>
       <c r="M9">
-        <v>0.3279225996383513</v>
+        <v>0.3380144698128268</v>
       </c>
       <c r="N9">
-        <v>0.3030218715966179</v>
+        <v>0.3121726040183876</v>
       </c>
       <c r="O9">
-        <v>0.2880862895153334</v>
+        <v>0.2966256404883859</v>
       </c>
       <c r="P9">
-        <v>0.3128808689613362</v>
+        <v>0.3279829061812469</v>
       </c>
     </row>
     <row r="10">
@@ -859,49 +859,49 @@
         </is>
       </c>
       <c r="B10">
-        <v>0.03665181473539902</v>
+        <v>0.03258287921827679</v>
       </c>
       <c r="C10">
-        <v>0.05628577439261095</v>
+        <v>0.04840509918131347</v>
       </c>
       <c r="D10">
-        <v>0.07953228149322988</v>
+        <v>0.06987281835985015</v>
       </c>
       <c r="E10">
-        <v>0.105798903683309</v>
+        <v>0.09467018317280484</v>
       </c>
       <c r="F10">
-        <v>0.1159180412054788</v>
+        <v>0.1042514967919818</v>
       </c>
       <c r="G10">
-        <v>0.1586367426170208</v>
+        <v>0.1467376936583614</v>
       </c>
       <c r="H10">
-        <v>0.154043078638593</v>
+        <v>0.1444833016899144</v>
       </c>
       <c r="I10">
-        <v>0.1768725918001022</v>
+        <v>0.1646863475009289</v>
       </c>
       <c r="J10">
-        <v>0.201443096085767</v>
+        <v>0.1904733374877577</v>
       </c>
       <c r="K10">
-        <v>0.239559532874127</v>
+        <v>0.2318053017539397</v>
       </c>
       <c r="L10">
-        <v>0.3143263816167946</v>
+        <v>0.3132985622114111</v>
       </c>
       <c r="M10">
-        <v>0.3287255644321678</v>
+        <v>0.3259999262818514</v>
       </c>
       <c r="N10">
-        <v>0.305957899414911</v>
+        <v>0.2982617955697388</v>
       </c>
       <c r="O10">
-        <v>0.2858912772492631</v>
+        <v>0.2795213812654095</v>
       </c>
       <c r="P10">
-        <v>0.309640969149139</v>
+        <v>0.3069780201791129</v>
       </c>
     </row>
     <row r="11">
@@ -911,49 +911,49 @@
         </is>
       </c>
       <c r="B11">
-        <v>0.02943670343140187</v>
+        <v>0.03195814924208484</v>
       </c>
       <c r="C11">
-        <v>0.04436967871586811</v>
+        <v>0.04807436303298496</v>
       </c>
       <c r="D11">
-        <v>0.06898496834499179</v>
+        <v>0.07646702928377247</v>
       </c>
       <c r="E11">
-        <v>0.09178087538883484</v>
+        <v>0.09890984121900093</v>
       </c>
       <c r="F11">
-        <v>0.1018863925885573</v>
+        <v>0.1084397969292065</v>
       </c>
       <c r="G11">
-        <v>0.1447170493603649</v>
+        <v>0.1531301786339189</v>
       </c>
       <c r="H11">
-        <v>0.1420629585734901</v>
+        <v>0.1487799360751102</v>
       </c>
       <c r="I11">
-        <v>0.1643225717168245</v>
+        <v>0.1718259521464344</v>
       </c>
       <c r="J11">
-        <v>0.189513495340914</v>
+        <v>0.1966909097431025</v>
       </c>
       <c r="K11">
-        <v>0.2367625841134867</v>
+        <v>0.2437259472587695</v>
       </c>
       <c r="L11">
-        <v>0.3203474901311356</v>
+        <v>0.3255736094606489</v>
       </c>
       <c r="M11">
-        <v>0.3405171297873616</v>
+        <v>0.3452236090682162</v>
       </c>
       <c r="N11">
-        <v>0.3138036420233187</v>
+        <v>0.316982883183121</v>
       </c>
       <c r="O11">
-        <v>0.291246229891501</v>
+        <v>0.2945209798730174</v>
       </c>
       <c r="P11">
-        <v>0.3089807841713521</v>
+        <v>0.3131142212374928</v>
       </c>
     </row>
     <row r="12">
@@ -963,49 +963,49 @@
         </is>
       </c>
       <c r="B12">
-        <v>0.03227910191146749</v>
+        <v>0.02662757026040141</v>
       </c>
       <c r="C12">
-        <v>0.0571366430713196</v>
+        <v>0.05010563448563021</v>
       </c>
       <c r="D12">
-        <v>0.1074900441578888</v>
+        <v>0.09920512733090703</v>
       </c>
       <c r="E12">
-        <v>0.1084015805845076</v>
+        <v>0.1032873551122767</v>
       </c>
       <c r="F12">
-        <v>0.1337629683858551</v>
+        <v>0.1298951977255466</v>
       </c>
       <c r="G12">
-        <v>0.1541274175519359</v>
+        <v>0.1490104973123918</v>
       </c>
       <c r="H12">
-        <v>0.1732071280108399</v>
+        <v>0.1715267589517402</v>
       </c>
       <c r="I12">
-        <v>0.2094265748443052</v>
+        <v>0.204022347329162</v>
       </c>
       <c r="J12">
-        <v>0.263748530639151</v>
+        <v>0.2602695329337946</v>
       </c>
       <c r="K12">
-        <v>0.3351302321201004</v>
+        <v>0.3261782587300513</v>
       </c>
       <c r="L12">
-        <v>0.4087952561474075</v>
+        <v>0.4007464169955338</v>
       </c>
       <c r="M12">
-        <v>0.4723676211755592</v>
+        <v>0.4573341291680177</v>
       </c>
       <c r="N12">
-        <v>0.4703767073919718</v>
+        <v>0.453935368909811</v>
       </c>
       <c r="O12">
-        <v>0.4774703295737838</v>
+        <v>0.4643715532216577</v>
       </c>
       <c r="P12">
-        <v>0.5008781533479849</v>
+        <v>0.4862828315215952</v>
       </c>
     </row>
     <row r="13">
@@ -1015,49 +1015,49 @@
         </is>
       </c>
       <c r="B13">
-        <v>0.03226257671489213</v>
+        <v>0.03371712492602391</v>
       </c>
       <c r="C13">
-        <v>0.06689624973505282</v>
+        <v>0.06737218793383171</v>
       </c>
       <c r="D13">
-        <v>0.1164728386033281</v>
+        <v>0.1201482099044672</v>
       </c>
       <c r="E13">
-        <v>0.1294380586723682</v>
+        <v>0.1321431086962526</v>
       </c>
       <c r="F13">
-        <v>0.1544373098435285</v>
+        <v>0.1591605079080769</v>
       </c>
       <c r="G13">
-        <v>0.1884425713842328</v>
+        <v>0.1926012246612051</v>
       </c>
       <c r="H13">
-        <v>0.2134520314773207</v>
+        <v>0.2180181788558483</v>
       </c>
       <c r="I13">
-        <v>0.261207526359195</v>
+        <v>0.2650067636399233</v>
       </c>
       <c r="J13">
-        <v>0.3044835498203436</v>
+        <v>0.3077171062557962</v>
       </c>
       <c r="K13">
-        <v>0.3803098622403024</v>
+        <v>0.3847318867053273</v>
       </c>
       <c r="L13">
-        <v>0.4163626656055447</v>
+        <v>0.417797596584599</v>
       </c>
       <c r="M13">
-        <v>0.4435467860419149</v>
+        <v>0.4476598144747379</v>
       </c>
       <c r="N13">
-        <v>0.4822425263522843</v>
+        <v>0.4836503958562189</v>
       </c>
       <c r="O13">
-        <v>0.5239669208278648</v>
+        <v>0.5274905236657393</v>
       </c>
       <c r="P13">
-        <v>0.5904013056850499</v>
+        <v>0.5840525554316015</v>
       </c>
     </row>
     <row r="14">
@@ -1067,49 +1067,49 @@
         </is>
       </c>
       <c r="B14">
-        <v>0.03430753391796204</v>
+        <v>0.03407746729557098</v>
       </c>
       <c r="C14">
-        <v>0.04941504576475148</v>
+        <v>0.04949142195881595</v>
       </c>
       <c r="D14">
-        <v>0.07906670358697288</v>
+        <v>0.07961800472087111</v>
       </c>
       <c r="E14">
-        <v>0.06695915744945158</v>
+        <v>0.06682289447282275</v>
       </c>
       <c r="F14">
-        <v>0.08882272339524966</v>
+        <v>0.08782521856678116</v>
       </c>
       <c r="G14">
-        <v>0.09807176259097883</v>
+        <v>0.09852443571089231</v>
       </c>
       <c r="H14">
-        <v>0.1267296877156396</v>
+        <v>0.1258462629514587</v>
       </c>
       <c r="I14">
-        <v>0.1320497700398704</v>
+        <v>0.133438898702566</v>
       </c>
       <c r="J14">
-        <v>0.1596572304932967</v>
+        <v>0.1634843455582866</v>
       </c>
       <c r="K14">
-        <v>0.2161559016948674</v>
+        <v>0.2178093447783616</v>
       </c>
       <c r="L14">
-        <v>0.2432393929814525</v>
+        <v>0.2466631474529916</v>
       </c>
       <c r="M14">
-        <v>0.3017659433290258</v>
+        <v>0.3038701027961287</v>
       </c>
       <c r="N14">
-        <v>0.323031151503207</v>
+        <v>0.3197193839723479</v>
       </c>
       <c r="O14">
-        <v>0.3213864052022006</v>
+        <v>0.3194019866738094</v>
       </c>
       <c r="P14">
-        <v>0.3001730599884674</v>
+        <v>0.2975960832270114</v>
       </c>
     </row>
     <row r="15">
@@ -1119,49 +1119,49 @@
         </is>
       </c>
       <c r="B15">
-        <v>0.0346623879062411</v>
+        <v>0.03708084235013714</v>
       </c>
       <c r="C15">
-        <v>0.05003623571485061</v>
+        <v>0.05383719702688922</v>
       </c>
       <c r="D15">
-        <v>0.07951790593534835</v>
+        <v>0.08261321231165575</v>
       </c>
       <c r="E15">
-        <v>0.06873832678699698</v>
+        <v>0.06916940577477537</v>
       </c>
       <c r="F15">
-        <v>0.08976671677226533</v>
+        <v>0.0890447408813172</v>
       </c>
       <c r="G15">
-        <v>0.1005869071332085</v>
+        <v>0.09929441977870401</v>
       </c>
       <c r="H15">
-        <v>0.1250157543323218</v>
+        <v>0.123137725497971</v>
       </c>
       <c r="I15">
-        <v>0.1310694512821418</v>
+        <v>0.1302281004328688</v>
       </c>
       <c r="J15">
-        <v>0.1572898245404964</v>
+        <v>0.1553433936154357</v>
       </c>
       <c r="K15">
-        <v>0.2104285720992844</v>
+        <v>0.2068283479294504</v>
       </c>
       <c r="L15">
-        <v>0.2284066415902615</v>
+        <v>0.2299360577771724</v>
       </c>
       <c r="M15">
-        <v>0.2859105923211259</v>
+        <v>0.2881546282203125</v>
       </c>
       <c r="N15">
-        <v>0.3024514312459178</v>
+        <v>0.3024748702606901</v>
       </c>
       <c r="O15">
-        <v>0.3021925983053839</v>
+        <v>0.3045265635876359</v>
       </c>
       <c r="P15">
-        <v>0.2845494905238056</v>
+        <v>0.2860380628987339</v>
       </c>
     </row>
     <row r="16">
@@ -1171,49 +1171,49 @@
         </is>
       </c>
       <c r="B16">
-        <v>0.0327787821513848</v>
+        <v>0.03607927966159136</v>
       </c>
       <c r="C16">
-        <v>0.04878739185809938</v>
+        <v>0.04980015022598189</v>
       </c>
       <c r="D16">
-        <v>0.07745732681823869</v>
+        <v>0.07869703648195647</v>
       </c>
       <c r="E16">
-        <v>0.06456030588142592</v>
+        <v>0.06605105478289297</v>
       </c>
       <c r="F16">
-        <v>0.08511764570534375</v>
+        <v>0.08699488876042616</v>
       </c>
       <c r="G16">
-        <v>0.09829545132143391</v>
+        <v>0.1006073752640202</v>
       </c>
       <c r="H16">
-        <v>0.1217516594706405</v>
+        <v>0.1260826084124926</v>
       </c>
       <c r="I16">
-        <v>0.1291428820353633</v>
+        <v>0.1302100766493065</v>
       </c>
       <c r="J16">
-        <v>0.1557803987430372</v>
+        <v>0.1596313954072567</v>
       </c>
       <c r="K16">
-        <v>0.2087556910956744</v>
+        <v>0.2124179720205227</v>
       </c>
       <c r="L16">
-        <v>0.2278916276802081</v>
+        <v>0.231241512491324</v>
       </c>
       <c r="M16">
-        <v>0.2781284983387365</v>
+        <v>0.2789236422220112</v>
       </c>
       <c r="N16">
-        <v>0.2988771947460988</v>
+        <v>0.3006085412958939</v>
       </c>
       <c r="O16">
-        <v>0.3035055641278729</v>
+        <v>0.3041021777228788</v>
       </c>
       <c r="P16">
-        <v>0.2901309412524014</v>
+        <v>0.2900538139773789</v>
       </c>
     </row>
     <row r="17">
@@ -1223,49 +1223,49 @@
         </is>
       </c>
       <c r="B17">
-        <v>0.03614674951309643</v>
+        <v>0.03800246048399997</v>
       </c>
       <c r="C17">
-        <v>0.05065745800114996</v>
+        <v>0.05417666340169641</v>
       </c>
       <c r="D17">
-        <v>0.08061808282425798</v>
+        <v>0.08670919778092401</v>
       </c>
       <c r="E17">
-        <v>0.06632991454775228</v>
+        <v>0.07180706004486659</v>
       </c>
       <c r="F17">
-        <v>0.08669905217807261</v>
+        <v>0.09391787358642933</v>
       </c>
       <c r="G17">
-        <v>0.09798770738570761</v>
+        <v>0.103592997225462</v>
       </c>
       <c r="H17">
-        <v>0.1233958400987966</v>
+        <v>0.1310937124452717</v>
       </c>
       <c r="I17">
-        <v>0.1283999958906622</v>
+        <v>0.1375577155191025</v>
       </c>
       <c r="J17">
-        <v>0.1561862466078274</v>
+        <v>0.1666917751982675</v>
       </c>
       <c r="K17">
-        <v>0.20739115445182</v>
+        <v>0.2205583320297063</v>
       </c>
       <c r="L17">
-        <v>0.2264544256150591</v>
+        <v>0.2388626619418713</v>
       </c>
       <c r="M17">
-        <v>0.2662229235095057</v>
+        <v>0.2827743643206381</v>
       </c>
       <c r="N17">
-        <v>0.2835693561789163</v>
+        <v>0.3018895773523294</v>
       </c>
       <c r="O17">
-        <v>0.276871010846737</v>
+        <v>0.2979061283184337</v>
       </c>
       <c r="P17">
-        <v>0.2709782279397898</v>
+        <v>0.2881598376746527</v>
       </c>
     </row>
     <row r="18">
@@ -1275,49 +1275,49 @@
         </is>
       </c>
       <c r="B18">
-        <v>0.0319073309725959</v>
+        <v>0.03235120036924144</v>
       </c>
       <c r="C18">
-        <v>0.05979851456119289</v>
+        <v>0.06753410244899527</v>
       </c>
       <c r="D18">
-        <v>0.1071509982320693</v>
+        <v>0.1164713221158369</v>
       </c>
       <c r="E18">
-        <v>0.1160620794776579</v>
+        <v>0.1263026397981757</v>
       </c>
       <c r="F18">
-        <v>0.1370129515582076</v>
+        <v>0.1476569384738198</v>
       </c>
       <c r="G18">
-        <v>0.1596653291197236</v>
+        <v>0.1706193291825312</v>
       </c>
       <c r="H18">
-        <v>0.1713454005269129</v>
+        <v>0.1822348591527574</v>
       </c>
       <c r="I18">
-        <v>0.2320610588348728</v>
+        <v>0.2422260408499206</v>
       </c>
       <c r="J18">
-        <v>0.2627860810297378</v>
+        <v>0.2732982565261891</v>
       </c>
       <c r="K18">
-        <v>0.3260039438165981</v>
+        <v>0.3415025758241477</v>
       </c>
       <c r="L18">
-        <v>0.3780765359445445</v>
+        <v>0.3936487515029565</v>
       </c>
       <c r="M18">
-        <v>0.4205877085681947</v>
+        <v>0.4364826941513417</v>
       </c>
       <c r="N18">
-        <v>0.4121876906756433</v>
+        <v>0.4242656027351261</v>
       </c>
       <c r="O18">
-        <v>0.4207856371956402</v>
+        <v>0.4278674130280917</v>
       </c>
       <c r="P18">
-        <v>0.4281644902431649</v>
+        <v>0.4352767702408521</v>
       </c>
     </row>
     <row r="19">
@@ -1327,49 +1327,49 @@
         </is>
       </c>
       <c r="B19">
-        <v>0.03275501264246605</v>
+        <v>0.0319208307583933</v>
       </c>
       <c r="C19">
-        <v>0.06100486814501305</v>
+        <v>0.06254062783437475</v>
       </c>
       <c r="D19">
-        <v>0.09520401679555546</v>
+        <v>0.1007156196518533</v>
       </c>
       <c r="E19">
-        <v>0.114180525409694</v>
+        <v>0.1188709678551647</v>
       </c>
       <c r="F19">
-        <v>0.1317350861605663</v>
+        <v>0.1320206691278274</v>
       </c>
       <c r="G19">
-        <v>0.1512297880962825</v>
+        <v>0.151101794403786</v>
       </c>
       <c r="H19">
-        <v>0.1730274833763141</v>
+        <v>0.1699894498512028</v>
       </c>
       <c r="I19">
-        <v>0.2207922891490931</v>
+        <v>0.2188821574412531</v>
       </c>
       <c r="J19">
-        <v>0.2915046888700138</v>
+        <v>0.2875635003294986</v>
       </c>
       <c r="K19">
-        <v>0.3392892060814803</v>
+        <v>0.3385909795228818</v>
       </c>
       <c r="L19">
-        <v>0.3885858523277236</v>
+        <v>0.3886137707715049</v>
       </c>
       <c r="M19">
-        <v>0.3921029182176735</v>
+        <v>0.3940297441456178</v>
       </c>
       <c r="N19">
-        <v>0.4054916861272432</v>
+        <v>0.4057993026603255</v>
       </c>
       <c r="O19">
-        <v>0.4030202380163012</v>
+        <v>0.4044828920788183</v>
       </c>
       <c r="P19">
-        <v>0.4323610673763688</v>
+        <v>0.4340465107742282</v>
       </c>
     </row>
     <row r="20">
@@ -1379,49 +1379,49 @@
         </is>
       </c>
       <c r="B20">
-        <v>0.03084336557175582</v>
+        <v>0.03067657966147397</v>
       </c>
       <c r="C20">
-        <v>0.06005782561826301</v>
+        <v>0.0550067382349565</v>
       </c>
       <c r="D20">
-        <v>0.09227459172989705</v>
+        <v>0.08817620963635642</v>
       </c>
       <c r="E20">
-        <v>0.136117892113841</v>
+        <v>0.1292564408630239</v>
       </c>
       <c r="F20">
-        <v>0.13439823411448</v>
+        <v>0.1301125409816998</v>
       </c>
       <c r="G20">
-        <v>0.1426132917346862</v>
+        <v>0.1418008047116341</v>
       </c>
       <c r="H20">
-        <v>0.1709774612463444</v>
+        <v>0.1674772479018339</v>
       </c>
       <c r="I20">
-        <v>0.2048710335545614</v>
+        <v>0.1974734017712729</v>
       </c>
       <c r="J20">
-        <v>0.2737935980224332</v>
+        <v>0.2666444186844295</v>
       </c>
       <c r="K20">
-        <v>0.3293824661094373</v>
+        <v>0.3238623090302267</v>
       </c>
       <c r="L20">
-        <v>0.3444615435184774</v>
+        <v>0.3463292314730976</v>
       </c>
       <c r="M20">
-        <v>0.3402073079652561</v>
+        <v>0.3423330270424865</v>
       </c>
       <c r="N20">
-        <v>0.3549549218886719</v>
+        <v>0.3547325528133944</v>
       </c>
       <c r="O20">
-        <v>0.3378435393218049</v>
+        <v>0.3444862200158649</v>
       </c>
       <c r="P20">
-        <v>0.3769337016491001</v>
+        <v>0.3823403830133975</v>
       </c>
     </row>
     <row r="21">
@@ -1431,49 +1431,49 @@
         </is>
       </c>
       <c r="B21">
-        <v>0.04254236831502756</v>
+        <v>0.03991441990872141</v>
       </c>
       <c r="C21">
-        <v>0.04179841366380704</v>
+        <v>0.04032254706485155</v>
       </c>
       <c r="D21">
-        <v>0.07749664378775128</v>
+        <v>0.07908230077403922</v>
       </c>
       <c r="E21">
-        <v>0.1034109607640937</v>
+        <v>0.10264668367906</v>
       </c>
       <c r="F21">
-        <v>0.1371336632970988</v>
+        <v>0.1434359717488874</v>
       </c>
       <c r="G21">
-        <v>0.172886586205347</v>
+        <v>0.1709967076142674</v>
       </c>
       <c r="H21">
-        <v>0.2539851607829859</v>
+        <v>0.2578371865294876</v>
       </c>
       <c r="I21">
-        <v>0.3136367807468124</v>
+        <v>0.3151147592322</v>
       </c>
       <c r="J21">
-        <v>0.35620240838857</v>
+        <v>0.3514874995280726</v>
       </c>
       <c r="K21">
-        <v>0.4055770705669217</v>
+        <v>0.3974881639308603</v>
       </c>
       <c r="L21">
-        <v>0.446974599225591</v>
+        <v>0.4412171094085257</v>
       </c>
       <c r="M21">
-        <v>0.5239416795064709</v>
+        <v>0.5170438582336637</v>
       </c>
       <c r="N21">
-        <v>0.6003204334720016</v>
+        <v>0.5903066948543884</v>
       </c>
       <c r="O21">
-        <v>0.6787852415818958</v>
+        <v>0.6598049828625032</v>
       </c>
       <c r="P21">
-        <v>0.8014467093326396</v>
+        <v>0.7752366356463811</v>
       </c>
     </row>
     <row r="22">
@@ -1483,49 +1483,49 @@
         </is>
       </c>
       <c r="B22">
-        <v>0.03986557118729472</v>
+        <v>0.04108913693888566</v>
       </c>
       <c r="C22">
-        <v>0.04094917378914087</v>
+        <v>0.04112732857815005</v>
       </c>
       <c r="D22">
-        <v>0.07639736239498451</v>
+        <v>0.0755224630484671</v>
       </c>
       <c r="E22">
-        <v>0.1037074096793711</v>
+        <v>0.1011044593048993</v>
       </c>
       <c r="F22">
-        <v>0.1477156492498897</v>
+        <v>0.1436658977566337</v>
       </c>
       <c r="G22">
-        <v>0.1575849526611391</v>
+        <v>0.1532217484779507</v>
       </c>
       <c r="H22">
-        <v>0.2577068512931724</v>
+        <v>0.2475920982809642</v>
       </c>
       <c r="I22">
-        <v>0.2989271179125701</v>
+        <v>0.2895788589776397</v>
       </c>
       <c r="J22">
-        <v>0.3282702728170293</v>
+        <v>0.3181787017923278</v>
       </c>
       <c r="K22">
-        <v>0.3752178964544692</v>
+        <v>0.3703477630011462</v>
       </c>
       <c r="L22">
-        <v>0.4331508250540173</v>
+        <v>0.425818052472266</v>
       </c>
       <c r="M22">
-        <v>0.5189539898395932</v>
+        <v>0.510598195291147</v>
       </c>
       <c r="N22">
-        <v>0.5735306388769179</v>
+        <v>0.5641824594890816</v>
       </c>
       <c r="O22">
-        <v>0.6613484778101766</v>
+        <v>0.6516171950226874</v>
       </c>
       <c r="P22">
-        <v>0.7799439663121622</v>
+        <v>0.7701878754141972</v>
       </c>
     </row>
     <row r="23">
@@ -1535,1297 +1535,1089 @@
         </is>
       </c>
       <c r="B23">
-        <v>0.03119579407752027</v>
+        <v>0.03066367342285536</v>
       </c>
       <c r="C23">
-        <v>0.07067335244263828</v>
+        <v>0.06820469493192216</v>
       </c>
       <c r="D23">
-        <v>0.08584484297450035</v>
+        <v>0.08831956072287772</v>
       </c>
       <c r="E23">
-        <v>0.09028116541107645</v>
+        <v>0.08668950191046998</v>
       </c>
       <c r="F23">
-        <v>0.1448728843979217</v>
+        <v>0.1411134550339741</v>
       </c>
       <c r="G23">
-        <v>0.2969840248129894</v>
+        <v>0.2965168831546518</v>
       </c>
       <c r="H23">
-        <v>0.3704374755699263</v>
+        <v>0.3757306598601834</v>
       </c>
       <c r="I23">
-        <v>0.412705742897538</v>
+        <v>0.4187387156659633</v>
       </c>
       <c r="J23">
-        <v>0.481139299971846</v>
+        <v>0.4884144141800291</v>
       </c>
       <c r="K23">
-        <v>0.5634121574544781</v>
+        <v>0.572818372431752</v>
       </c>
       <c r="L23">
-        <v>0.6507757094894966</v>
+        <v>0.6538953438848332</v>
       </c>
       <c r="M23">
-        <v>0.7639285382772716</v>
+        <v>0.7578106817772428</v>
       </c>
       <c r="N23">
-        <v>0.8618077221279935</v>
+        <v>0.8593875640568653</v>
       </c>
       <c r="O23">
-        <v>0.9532160724685619</v>
+        <v>0.9461339798172695</v>
       </c>
       <c r="P23">
-        <v>1.101764916474662</v>
+        <v>1.098640778989573</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>adj_red_c(950,20,1)_snv_sder_c(1,3,15)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_msc_</t>
         </is>
       </c>
       <c r="B24">
-        <v>0.06429356992538277</v>
+        <v>0.02436455273984073</v>
       </c>
       <c r="C24">
-        <v>0.1718434889931484</v>
+        <v>0.04004187946965698</v>
       </c>
       <c r="D24">
-        <v>0.1730821548806494</v>
+        <v>0.05376119875855134</v>
       </c>
       <c r="E24">
-        <v>0.3091021483416585</v>
+        <v>0.05901575426726346</v>
       </c>
       <c r="F24">
-        <v>0.4919700525404406</v>
+        <v>0.07623643335197661</v>
       </c>
       <c r="G24">
-        <v>0.5564741237582431</v>
+        <v>0.08096259130229744</v>
       </c>
       <c r="H24">
-        <v>0.6647249290979376</v>
+        <v>0.09704420649509649</v>
       </c>
       <c r="I24">
-        <v>0.7911306317317975</v>
+        <v>0.1260381056802253</v>
       </c>
       <c r="J24">
-        <v>0.9032907030788037</v>
+        <v>0.1704343657233319</v>
       </c>
       <c r="K24">
-        <v>0.9523188662547816</v>
+        <v>0.2361934233145548</v>
       </c>
       <c r="L24">
-        <v>1.038385619123866</v>
+        <v>0.2909669775789763</v>
       </c>
       <c r="M24">
-        <v>1.102437611509808</v>
+        <v>0.3683770862710828</v>
       </c>
       <c r="N24">
-        <v>1.284924028405274</v>
+        <v>0.4440752188926687</v>
       </c>
       <c r="O24">
-        <v>1.361378212325903</v>
+        <v>0.5378146275998827</v>
       </c>
       <c r="P24">
-        <v>1.434808037971021</v>
+        <v>0.6390995357178531</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>adj_red_c(950,20,1)_snv_sder_c(2,3,15)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_</t>
         </is>
       </c>
       <c r="B25">
-        <v>0.08636863506488909</v>
+        <v>0.02800038830978935</v>
       </c>
       <c r="C25">
-        <v>0.1785058114224123</v>
+        <v>0.04158393610804378</v>
       </c>
       <c r="D25">
-        <v>0.2397124077492794</v>
+        <v>0.05602504405198827</v>
       </c>
       <c r="E25">
-        <v>0.3297735771674824</v>
+        <v>0.05544293768453967</v>
       </c>
       <c r="F25">
-        <v>0.4649681729490988</v>
+        <v>0.06608400785509039</v>
       </c>
       <c r="G25">
-        <v>0.6329866337389809</v>
+        <v>0.06786475737502473</v>
       </c>
       <c r="H25">
-        <v>0.7376679647290628</v>
+        <v>0.07657956265130461</v>
       </c>
       <c r="I25">
-        <v>0.8659693927357853</v>
+        <v>0.1419144014658628</v>
       </c>
       <c r="J25">
-        <v>0.9448898588646131</v>
+        <v>0.1526486706778961</v>
       </c>
       <c r="K25">
-        <v>1.052220955310899</v>
+        <v>0.1781570014670971</v>
       </c>
       <c r="L25">
-        <v>1.190903488134985</v>
+        <v>0.238460949100172</v>
       </c>
       <c r="M25">
-        <v>1.32481382603883</v>
+        <v>0.2797439732094325</v>
       </c>
       <c r="N25">
-        <v>1.434815853637472</v>
+        <v>0.3552642268113624</v>
       </c>
       <c r="O25">
-        <v>1.514416360579105</v>
+        <v>0.4066154927815099</v>
       </c>
       <c r="P25">
-        <v>1.564469265029184</v>
+        <v>0.5243682275573601</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>adj_red_c(950,750,1)_snv_sder_c(1,3,15)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_</t>
         </is>
       </c>
       <c r="B26">
-        <v>0.07099608995203563</v>
+        <v>0.02721393778244696</v>
       </c>
       <c r="C26">
-        <v>0.1305647332914787</v>
+        <v>0.04222399974982372</v>
       </c>
       <c r="D26">
-        <v>0.1538284712387467</v>
+        <v>0.06432014278373754</v>
       </c>
       <c r="E26">
-        <v>0.1957887781132355</v>
+        <v>0.05502325399638774</v>
       </c>
       <c r="F26">
-        <v>0.3066913078030147</v>
+        <v>0.07412131396027588</v>
       </c>
       <c r="G26">
-        <v>0.3848355888006352</v>
+        <v>0.07998660777224631</v>
       </c>
       <c r="H26">
-        <v>0.5275173057631911</v>
+        <v>0.08777210595504314</v>
       </c>
       <c r="I26">
-        <v>0.611490359518164</v>
+        <v>0.1162056132398911</v>
       </c>
       <c r="J26">
-        <v>0.6098319202350806</v>
+        <v>0.1992064673671601</v>
       </c>
       <c r="K26">
-        <v>0.6504318635369117</v>
+        <v>0.2359137705451837</v>
       </c>
       <c r="L26">
-        <v>0.7283879683602493</v>
+        <v>0.3078880182275159</v>
       </c>
       <c r="M26">
-        <v>0.9659049667784367</v>
+        <v>0.3562440598048002</v>
       </c>
       <c r="N26">
-        <v>0.9404901413267803</v>
+        <v>0.4229402310784229</v>
       </c>
       <c r="O26">
-        <v>0.9689610505908364</v>
+        <v>0.5194578976542235</v>
       </c>
       <c r="P26">
-        <v>0.9798493413630229</v>
+        <v>0.5954744578896132</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>adj_red_c(950,750,1)_snv_sder_c(2,3,15)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
         </is>
       </c>
       <c r="B27">
-        <v>0.08293828495322139</v>
+        <v>0.02825983699144829</v>
       </c>
       <c r="C27">
-        <v>0.1551369551031071</v>
+        <v>0.04375010188381845</v>
       </c>
       <c r="D27">
-        <v>0.2950946173986136</v>
+        <v>0.0655105905524328</v>
       </c>
       <c r="E27">
-        <v>0.2508339865950227</v>
+        <v>0.05427369531281157</v>
       </c>
       <c r="F27">
-        <v>0.3976994984763505</v>
+        <v>0.07532141532361825</v>
       </c>
       <c r="G27">
-        <v>0.4801255719233001</v>
+        <v>0.07908934701487558</v>
       </c>
       <c r="H27">
-        <v>0.4789997619543704</v>
+        <v>0.0848564974667505</v>
       </c>
       <c r="I27">
-        <v>0.5927997049151338</v>
+        <v>0.1007549869863928</v>
       </c>
       <c r="J27">
-        <v>0.699536214655625</v>
+        <v>0.1476707489417562</v>
       </c>
       <c r="K27">
-        <v>0.7814298454580489</v>
+        <v>0.1837719266354383</v>
       </c>
       <c r="L27">
-        <v>0.8865404659905558</v>
+        <v>0.2334442534141781</v>
       </c>
       <c r="M27">
-        <v>1.001558242555011</v>
+        <v>0.2918345594427117</v>
       </c>
       <c r="N27">
-        <v>0.9235305136833122</v>
+        <v>0.3133845129696708</v>
       </c>
       <c r="O27">
-        <v>1.018379213161983</v>
+        <v>0.3236477663892239</v>
       </c>
       <c r="P27">
-        <v>1.066093485894003</v>
+        <v>0.391277511686295</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_msc_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,21)_</t>
         </is>
       </c>
       <c r="B28">
-        <v>0.02419811460020116</v>
+        <v>0.02922709518082878</v>
       </c>
       <c r="C28">
-        <v>0.03874917519096599</v>
+        <v>0.04376724579220403</v>
       </c>
       <c r="D28">
-        <v>0.05054808877292316</v>
+        <v>0.05851606090990813</v>
       </c>
       <c r="E28">
-        <v>0.05465657739608876</v>
+        <v>0.05716156701625874</v>
       </c>
       <c r="F28">
-        <v>0.07104628719727846</v>
+        <v>0.06567001728069155</v>
       </c>
       <c r="G28">
-        <v>0.07871161683785055</v>
+        <v>0.06509393627158144</v>
       </c>
       <c r="H28">
-        <v>0.09530580085734419</v>
+        <v>0.07186487672176955</v>
       </c>
       <c r="I28">
-        <v>0.1259326231138911</v>
+        <v>0.1198882874793528</v>
       </c>
       <c r="J28">
-        <v>0.1707190910815088</v>
+        <v>0.1176295169200855</v>
       </c>
       <c r="K28">
-        <v>0.2347452762926598</v>
+        <v>0.1239825806577172</v>
       </c>
       <c r="L28">
-        <v>0.288136488446498</v>
+        <v>0.1565753996451918</v>
       </c>
       <c r="M28">
-        <v>0.3633661347205085</v>
+        <v>0.2170634945385046</v>
       </c>
       <c r="N28">
-        <v>0.4405836265817638</v>
+        <v>0.2424945825030896</v>
       </c>
       <c r="O28">
-        <v>0.5310917632196488</v>
+        <v>0.260833341833714</v>
       </c>
       <c r="P28">
-        <v>0.633931090483314</v>
+        <v>0.3088164423353336</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,25)_</t>
         </is>
       </c>
       <c r="B29">
-        <v>0.02911976786186676</v>
+        <v>0.02777252513467954</v>
       </c>
       <c r="C29">
-        <v>0.04308994485595652</v>
+        <v>0.04262442486744566</v>
       </c>
       <c r="D29">
-        <v>0.05682926094832241</v>
+        <v>0.05534329088651557</v>
       </c>
       <c r="E29">
-        <v>0.05862198916775474</v>
+        <v>0.05489900173590756</v>
       </c>
       <c r="F29">
-        <v>0.06840202941326334</v>
+        <v>0.06390703639921691</v>
       </c>
       <c r="G29">
-        <v>0.06940327448405204</v>
+        <v>0.06313613195999379</v>
       </c>
       <c r="H29">
-        <v>0.07731716842614444</v>
+        <v>0.06992227350072755</v>
       </c>
       <c r="I29">
-        <v>0.1471194075381591</v>
+        <v>0.1111996196480053</v>
       </c>
       <c r="J29">
-        <v>0.1540609321222446</v>
+        <v>0.1124333721647596</v>
       </c>
       <c r="K29">
-        <v>0.1811043103256175</v>
+        <v>0.1162851541418534</v>
       </c>
       <c r="L29">
-        <v>0.2357684345912846</v>
+        <v>0.1419408886047508</v>
       </c>
       <c r="M29">
-        <v>0.2787746039449787</v>
+        <v>0.1980151183634487</v>
       </c>
       <c r="N29">
-        <v>0.3542977661509743</v>
+        <v>0.2282452600961462</v>
       </c>
       <c r="O29">
-        <v>0.404090564075623</v>
+        <v>0.2479299198937591</v>
       </c>
       <c r="P29">
-        <v>0.5275327294696023</v>
+        <v>0.2821010463622641</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,27)_</t>
         </is>
       </c>
       <c r="B30">
-        <v>0.02790687255925328</v>
+        <v>0.02779783139305392</v>
       </c>
       <c r="C30">
-        <v>0.04309963867034317</v>
+        <v>0.04287292102591289</v>
       </c>
       <c r="D30">
-        <v>0.06584151960420193</v>
+        <v>0.05757078565994012</v>
       </c>
       <c r="E30">
-        <v>0.05690621642872562</v>
+        <v>0.05501118433342278</v>
       </c>
       <c r="F30">
-        <v>0.07456041295527593</v>
+        <v>0.06150268612125132</v>
       </c>
       <c r="G30">
-        <v>0.08024555820269064</v>
+        <v>0.06276808256331368</v>
       </c>
       <c r="H30">
-        <v>0.09121027323173792</v>
+        <v>0.06646210494125948</v>
       </c>
       <c r="I30">
-        <v>0.1181303040587351</v>
+        <v>0.1112897646656036</v>
       </c>
       <c r="J30">
-        <v>0.2012125532963598</v>
+        <v>0.1119333121447454</v>
       </c>
       <c r="K30">
-        <v>0.2372506593022026</v>
+        <v>0.1162992394108692</v>
       </c>
       <c r="L30">
-        <v>0.3083795658253702</v>
+        <v>0.1424872173623019</v>
       </c>
       <c r="M30">
-        <v>0.3582205181553126</v>
+        <v>0.1919017999939874</v>
       </c>
       <c r="N30">
-        <v>0.4264661992245584</v>
+        <v>0.2223142941566322</v>
       </c>
       <c r="O30">
-        <v>0.5229164651107947</v>
+        <v>0.2428817661142054</v>
       </c>
       <c r="P30">
-        <v>0.5985345919458491</v>
+        <v>0.2699778203777569</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,31)_</t>
         </is>
       </c>
       <c r="B31">
-        <v>0.02731403279390598</v>
+        <v>0.02760572475236278</v>
       </c>
       <c r="C31">
-        <v>0.04200372167207533</v>
+        <v>0.04133906829219958</v>
       </c>
       <c r="D31">
-        <v>0.06481457411673608</v>
+        <v>0.05627699110678508</v>
       </c>
       <c r="E31">
-        <v>0.05517950044864461</v>
+        <v>0.0558701247532245</v>
       </c>
       <c r="F31">
-        <v>0.07477656241776665</v>
+        <v>0.06612390329156614</v>
       </c>
       <c r="G31">
-        <v>0.07654903437114591</v>
+        <v>0.06333492114313433</v>
       </c>
       <c r="H31">
-        <v>0.08354210092316516</v>
+        <v>0.07089970883302155</v>
       </c>
       <c r="I31">
-        <v>0.1000809448099598</v>
+        <v>0.1134019070338376</v>
       </c>
       <c r="J31">
-        <v>0.1470982648923325</v>
+        <v>0.1135426922134989</v>
       </c>
       <c r="K31">
-        <v>0.1833264671486865</v>
+        <v>0.1162063505001537</v>
       </c>
       <c r="L31">
-        <v>0.2303312546859776</v>
+        <v>0.1389349027533181</v>
       </c>
       <c r="M31">
-        <v>0.2895448073381215</v>
+        <v>0.182948120765162</v>
       </c>
       <c r="N31">
-        <v>0.3116597451163819</v>
+        <v>0.214909554795907</v>
       </c>
       <c r="O31">
-        <v>0.3233654297474245</v>
+        <v>0.2367024092857021</v>
       </c>
       <c r="P31">
-        <v>0.3888415404569771</v>
+        <v>0.2498919935523575</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,21)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
         </is>
       </c>
       <c r="B32">
-        <v>0.02782457371541258</v>
+        <v>0.02535968063135852</v>
       </c>
       <c r="C32">
-        <v>0.0419969461340931</v>
+        <v>0.03916568932359199</v>
       </c>
       <c r="D32">
-        <v>0.05552535794414881</v>
+        <v>0.05266297160816646</v>
       </c>
       <c r="E32">
-        <v>0.05623439740258696</v>
+        <v>0.05441501773413471</v>
       </c>
       <c r="F32">
-        <v>0.06729478443585635</v>
+        <v>0.06330419830295619</v>
       </c>
       <c r="G32">
-        <v>0.06629928013400688</v>
+        <v>0.06415928497187628</v>
       </c>
       <c r="H32">
-        <v>0.07444087804325916</v>
+        <v>0.06990148773013838</v>
       </c>
       <c r="I32">
-        <v>0.1199910658375228</v>
+        <v>0.1171009766734481</v>
       </c>
       <c r="J32">
-        <v>0.1189935019666026</v>
+        <v>0.1185676812257576</v>
       </c>
       <c r="K32">
-        <v>0.1241797106560119</v>
+        <v>0.1274149918565216</v>
       </c>
       <c r="L32">
-        <v>0.1535926930238583</v>
+        <v>0.1693506817819532</v>
       </c>
       <c r="M32">
-        <v>0.2143145445172301</v>
+        <v>0.229420163598945</v>
       </c>
       <c r="N32">
-        <v>0.2413024513530871</v>
+        <v>0.2492143053687846</v>
       </c>
       <c r="O32">
-        <v>0.2631233178038774</v>
+        <v>0.272150323457209</v>
       </c>
       <c r="P32">
-        <v>0.3120360426513248</v>
+        <v>0.3422128938101784</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,25)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,17)_</t>
         </is>
       </c>
       <c r="B33">
-        <v>0.0266099805989326</v>
+        <v>0.02858777030358683</v>
       </c>
       <c r="C33">
-        <v>0.04167573464929941</v>
+        <v>0.0437178967361993</v>
       </c>
       <c r="D33">
-        <v>0.05440012151873386</v>
+        <v>0.05866888809778492</v>
       </c>
       <c r="E33">
-        <v>0.05399539651924079</v>
+        <v>0.05741202630346676</v>
       </c>
       <c r="F33">
-        <v>0.06549627677866299</v>
+        <v>0.0675870727107144</v>
       </c>
       <c r="G33">
-        <v>0.06553988631250696</v>
+        <v>0.06732236356873478</v>
       </c>
       <c r="H33">
-        <v>0.07121324492046399</v>
+        <v>0.07409223157499067</v>
       </c>
       <c r="I33">
-        <v>0.1135858728243196</v>
+        <v>0.123403480478995</v>
       </c>
       <c r="J33">
-        <v>0.1132410638480256</v>
+        <v>0.1256656396916785</v>
       </c>
       <c r="K33">
-        <v>0.1164255630642757</v>
+        <v>0.1337440994566383</v>
       </c>
       <c r="L33">
-        <v>0.14349109657345</v>
+        <v>0.1709384480274898</v>
       </c>
       <c r="M33">
-        <v>0.1974072903807988</v>
+        <v>0.2343458807495462</v>
       </c>
       <c r="N33">
-        <v>0.2246695058191379</v>
+        <v>0.2569019329308749</v>
       </c>
       <c r="O33">
-        <v>0.2449621878686425</v>
+        <v>0.2751731994042688</v>
       </c>
       <c r="P33">
-        <v>0.28017818874537</v>
+        <v>0.344167938166662</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,27)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,19)_</t>
         </is>
       </c>
       <c r="B34">
-        <v>0.0253477351797341</v>
+        <v>0.02780176808564438</v>
       </c>
       <c r="C34">
-        <v>0.04064638490916772</v>
+        <v>0.04261716977238139</v>
       </c>
       <c r="D34">
-        <v>0.05529237445211344</v>
+        <v>0.05723440985096673</v>
       </c>
       <c r="E34">
-        <v>0.05397707625026882</v>
+        <v>0.05603849770954517</v>
       </c>
       <c r="F34">
-        <v>0.0636851236331093</v>
+        <v>0.06480905366754164</v>
       </c>
       <c r="G34">
-        <v>0.06341635260706313</v>
+        <v>0.06415605613242537</v>
       </c>
       <c r="H34">
-        <v>0.07024296170532429</v>
+        <v>0.06991116885515403</v>
       </c>
       <c r="I34">
-        <v>0.1120856901749948</v>
+        <v>0.1151810568381963</v>
       </c>
       <c r="J34">
-        <v>0.1119153203622284</v>
+        <v>0.1183636961203878</v>
       </c>
       <c r="K34">
-        <v>0.1158373423872159</v>
+        <v>0.1238334086418369</v>
       </c>
       <c r="L34">
-        <v>0.1414701862374984</v>
+        <v>0.1608253120114997</v>
       </c>
       <c r="M34">
-        <v>0.1902474066979764</v>
+        <v>0.2267111187871315</v>
       </c>
       <c r="N34">
-        <v>0.2205378726565311</v>
+        <v>0.2488167994372904</v>
       </c>
       <c r="O34">
-        <v>0.2398244488050976</v>
+        <v>0.2677157678473733</v>
       </c>
       <c r="P34">
-        <v>0.2714538919106422</v>
+        <v>0.3239671343211638</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,31)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
         </is>
       </c>
       <c r="B35">
-        <v>0.02903239182969874</v>
+        <v>0.02668737950038269</v>
       </c>
       <c r="C35">
-        <v>0.04346613479262584</v>
+        <v>0.04206381183176833</v>
       </c>
       <c r="D35">
-        <v>0.05615203996506546</v>
+        <v>0.05620652887282895</v>
       </c>
       <c r="E35">
-        <v>0.05593516050042679</v>
+        <v>0.05570337321287222</v>
       </c>
       <c r="F35">
-        <v>0.06522806382221902</v>
+        <v>0.06486621413602545</v>
       </c>
       <c r="G35">
-        <v>0.06266895416420781</v>
+        <v>0.06573004696057805</v>
       </c>
       <c r="H35">
-        <v>0.06900664685649016</v>
+        <v>0.07062200385841322</v>
       </c>
       <c r="I35">
-        <v>0.1116016166042655</v>
+        <v>0.1164843259094805</v>
       </c>
       <c r="J35">
-        <v>0.1115552335179161</v>
+        <v>0.1157797425056116</v>
       </c>
       <c r="K35">
-        <v>0.1145636564214557</v>
+        <v>0.1231015547688321</v>
       </c>
       <c r="L35">
-        <v>0.1388787925848785</v>
+        <v>0.1561880474264955</v>
       </c>
       <c r="M35">
-        <v>0.1860633131889536</v>
+        <v>0.2161451768535432</v>
       </c>
       <c r="N35">
-        <v>0.2175681920576297</v>
+        <v>0.2433297588001117</v>
       </c>
       <c r="O35">
-        <v>0.2417851354215649</v>
+        <v>0.2573595863608523</v>
       </c>
       <c r="P35">
-        <v>0.2544995242470547</v>
+        <v>0.311871606965279</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
         </is>
       </c>
       <c r="B36">
-        <v>0.02628792227927612</v>
+        <v>0.02855514290605721</v>
       </c>
       <c r="C36">
-        <v>0.03966455786513523</v>
+        <v>0.04332412510446504</v>
       </c>
       <c r="D36">
-        <v>0.05380880740643301</v>
+        <v>0.05702502744479665</v>
       </c>
       <c r="E36">
-        <v>0.05281096078529424</v>
+        <v>0.05800797218297982</v>
       </c>
       <c r="F36">
-        <v>0.06269805810997353</v>
+        <v>0.06551165551612959</v>
       </c>
       <c r="G36">
-        <v>0.0629437101030883</v>
+        <v>0.06513587111255803</v>
       </c>
       <c r="H36">
-        <v>0.06800495330924639</v>
+        <v>0.0725863208228319</v>
       </c>
       <c r="I36">
-        <v>0.112453514463432</v>
+        <v>0.1163346942380303</v>
       </c>
       <c r="J36">
-        <v>0.1158504314386174</v>
+        <v>0.1179404735113038</v>
       </c>
       <c r="K36">
-        <v>0.123309936208694</v>
+        <v>0.1212493154757742</v>
       </c>
       <c r="L36">
-        <v>0.1646393275049938</v>
+        <v>0.1468117135376114</v>
       </c>
       <c r="M36">
-        <v>0.221963498734347</v>
+        <v>0.1888717314797108</v>
       </c>
       <c r="N36">
-        <v>0.2400142249169225</v>
+        <v>0.2189219261006596</v>
       </c>
       <c r="O36">
-        <v>0.2607591600935986</v>
+        <v>0.2393201693637729</v>
       </c>
       <c r="P36">
-        <v>0.3369868810914933</v>
+        <v>0.2584927415706937</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,17)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
         </is>
       </c>
       <c r="B37">
-        <v>0.02905604336530332</v>
+        <v>0.03095926026395779</v>
       </c>
       <c r="C37">
-        <v>0.04384565490702763</v>
+        <v>0.127648675060137</v>
       </c>
       <c r="D37">
-        <v>0.05689603116537523</v>
+        <v>0.07657095984722195</v>
       </c>
       <c r="E37">
-        <v>0.05552891641799174</v>
+        <v>0.09086708723224768</v>
       </c>
       <c r="F37">
-        <v>0.06577940163842255</v>
+        <v>0.1581404801535773</v>
       </c>
       <c r="G37">
-        <v>0.06502382980586607</v>
+        <v>0.194486459692497</v>
       </c>
       <c r="H37">
-        <v>0.07108769553398753</v>
+        <v>0.1983444145450097</v>
       </c>
       <c r="I37">
-        <v>0.1166470017047363</v>
+        <v>0.2312276193868913</v>
       </c>
       <c r="J37">
-        <v>0.1185477603620819</v>
+        <v>0.3003514278947433</v>
       </c>
       <c r="K37">
-        <v>0.1245349806499052</v>
+        <v>0.3649245218069972</v>
       </c>
       <c r="L37">
-        <v>0.163321142607449</v>
+        <v>0.4168147951644312</v>
       </c>
       <c r="M37">
-        <v>0.2258309762870601</v>
+        <v>0.4612562410977144</v>
       </c>
       <c r="N37">
-        <v>0.24776015214932</v>
+        <v>0.4993429564040833</v>
       </c>
       <c r="O37">
-        <v>0.2669383976898932</v>
+        <v>0.5386709559865195</v>
       </c>
       <c r="P37">
-        <v>0.3355575116351802</v>
+        <v>0.5645465474697163</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,19)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,25)_</t>
         </is>
       </c>
       <c r="B38">
-        <v>0.02763914563790659</v>
+        <v>0.02917081548442679</v>
       </c>
       <c r="C38">
-        <v>0.04264484167234572</v>
+        <v>0.1064331264706392</v>
       </c>
       <c r="D38">
-        <v>0.05878006423429627</v>
+        <v>0.06415899369254596</v>
       </c>
       <c r="E38">
-        <v>0.0570365748076086</v>
+        <v>0.0756979434753815</v>
       </c>
       <c r="F38">
-        <v>0.06605268278655474</v>
+        <v>0.1117076013894123</v>
       </c>
       <c r="G38">
-        <v>0.06693229477655727</v>
+        <v>0.1695925069377491</v>
       </c>
       <c r="H38">
-        <v>0.07606014520842763</v>
+        <v>0.1427323724562684</v>
       </c>
       <c r="I38">
-        <v>0.1210306264427237</v>
+        <v>0.1781818013279175</v>
       </c>
       <c r="J38">
-        <v>0.1198074568311024</v>
+        <v>0.226887052223077</v>
       </c>
       <c r="K38">
-        <v>0.1260369267471414</v>
+        <v>0.2633362453671033</v>
       </c>
       <c r="L38">
-        <v>0.1600354803481153</v>
+        <v>0.2869036359677694</v>
       </c>
       <c r="M38">
-        <v>0.2243452572562812</v>
+        <v>0.342567271337875</v>
       </c>
       <c r="N38">
-        <v>0.2490923802193709</v>
+        <v>0.4041990934639346</v>
       </c>
       <c r="O38">
-        <v>0.26880251663857</v>
+        <v>0.4714549828104936</v>
       </c>
       <c r="P38">
-        <v>0.3259008496205419</v>
+        <v>0.5405265987670398</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
         </is>
       </c>
       <c r="B39">
-        <v>0.02921918249039279</v>
+        <v>0.02675932153924265</v>
       </c>
       <c r="C39">
-        <v>0.04359883719705027</v>
+        <v>0.1003896855764952</v>
       </c>
       <c r="D39">
-        <v>0.05812038669594544</v>
+        <v>0.05763107095998787</v>
       </c>
       <c r="E39">
-        <v>0.05673759117386634</v>
+        <v>0.06930161465554885</v>
       </c>
       <c r="F39">
-        <v>0.06590024020476049</v>
+        <v>0.09546702465881807</v>
       </c>
       <c r="G39">
-        <v>0.06585421692437066</v>
+        <v>0.1346866033000572</v>
       </c>
       <c r="H39">
-        <v>0.07211651268987029</v>
+        <v>0.1215346653158812</v>
       </c>
       <c r="I39">
-        <v>0.1150080463000205</v>
+        <v>0.1517620830685323</v>
       </c>
       <c r="J39">
-        <v>0.1155229846419782</v>
+        <v>0.1971162187749933</v>
       </c>
       <c r="K39">
-        <v>0.1198258299827544</v>
+        <v>0.2477569396280841</v>
       </c>
       <c r="L39">
-        <v>0.1565878405499468</v>
+        <v>0.2831505361377818</v>
       </c>
       <c r="M39">
-        <v>0.218986989321039</v>
+        <v>0.3508512872056074</v>
       </c>
       <c r="N39">
-        <v>0.2474176998056722</v>
+        <v>0.3881496501338847</v>
       </c>
       <c r="O39">
-        <v>0.2664570665414451</v>
+        <v>0.4200036858420823</v>
       </c>
       <c r="P39">
-        <v>0.3246828665444654</v>
+        <v>0.4689962877249225</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(2,3,21)_</t>
         </is>
       </c>
       <c r="B40">
-        <v>0.02710787645125923</v>
+        <v>0.0332478409649547</v>
       </c>
       <c r="C40">
-        <v>0.04093450555344857</v>
+        <v>0.0552913474036093</v>
       </c>
       <c r="D40">
-        <v>0.05455861789129235</v>
+        <v>0.08611280726644677</v>
       </c>
       <c r="E40">
-        <v>0.05468845728792548</v>
+        <v>0.1004405204674275</v>
       </c>
       <c r="F40">
-        <v>0.06592589595026188</v>
+        <v>0.1232851975096027</v>
       </c>
       <c r="G40">
-        <v>0.06242169979493661</v>
+        <v>0.1504877914110365</v>
       </c>
       <c r="H40">
-        <v>0.06952365122217385</v>
+        <v>0.203324023331945</v>
       </c>
       <c r="I40">
-        <v>0.1118350668976633</v>
+        <v>0.2336514857737292</v>
       </c>
       <c r="J40">
-        <v>0.1139835540074299</v>
+        <v>0.2754665910544241</v>
       </c>
       <c r="K40">
-        <v>0.1158718924926467</v>
+        <v>0.3383676247854216</v>
       </c>
       <c r="L40">
-        <v>0.1402335535675159</v>
+        <v>0.4248563313407203</v>
       </c>
       <c r="M40">
-        <v>0.1861448826539139</v>
+        <v>0.5187440670124213</v>
       </c>
       <c r="N40">
-        <v>0.2176489840436018</v>
+        <v>0.5868487461004555</v>
       </c>
       <c r="O40">
-        <v>0.2387119273735161</v>
+        <v>0.6684985217457363</v>
       </c>
       <c r="P40">
-        <v>0.2572743094627755</v>
+        <v>0.7492231711644213</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
+          <t>adj_snv_sder_c(1,3,5)_</t>
         </is>
       </c>
       <c r="B41">
-        <v>0.02920307087371043</v>
+        <v>0.04200480871581885</v>
       </c>
       <c r="C41">
-        <v>0.1226741034697751</v>
+        <v>0.06591349332937535</v>
       </c>
       <c r="D41">
-        <v>0.07654632644315662</v>
+        <v>0.1588728989797139</v>
       </c>
       <c r="E41">
-        <v>0.08993389173588318</v>
+        <v>0.2658881743308639</v>
       </c>
       <c r="F41">
-        <v>0.1592131701979551</v>
+        <v>0.3963647352913469</v>
       </c>
       <c r="G41">
-        <v>0.1919084043113735</v>
+        <v>0.434643526612556</v>
       </c>
       <c r="H41">
-        <v>0.1950145089149274</v>
+        <v>0.4109346260598987</v>
       </c>
       <c r="I41">
-        <v>0.2255075596444307</v>
+        <v>0.4116053603454055</v>
       </c>
       <c r="J41">
-        <v>0.2921711318424492</v>
+        <v>0.4424333522142001</v>
       </c>
       <c r="K41">
-        <v>0.3564092067520778</v>
+        <v>0.5098591297132229</v>
       </c>
       <c r="L41">
-        <v>0.4072260815408846</v>
+        <v>0.6219897558616714</v>
       </c>
       <c r="M41">
-        <v>0.4526067604785843</v>
+        <v>0.6870291648022864</v>
       </c>
       <c r="N41">
-        <v>0.4887867100253367</v>
+        <v>0.7429410735501744</v>
       </c>
       <c r="O41">
-        <v>0.5284714211449755</v>
+        <v>0.8031383820665268</v>
       </c>
       <c r="P41">
-        <v>0.5539958320559889</v>
+        <v>0.8168209914899461</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,25)_</t>
+          <t>adj_snv_sder_c(2,3,15)_</t>
         </is>
       </c>
       <c r="B42">
-        <v>0.02951425895158977</v>
+        <v>0.04680551452608728</v>
       </c>
       <c r="C42">
-        <v>0.1046184918847359</v>
+        <v>0.05049349899031597</v>
       </c>
       <c r="D42">
-        <v>0.06165640354104096</v>
+        <v>0.1264880802357686</v>
       </c>
       <c r="E42">
-        <v>0.07196022491966325</v>
+        <v>0.1700117419018249</v>
       </c>
       <c r="F42">
-        <v>0.1112752331928549</v>
+        <v>0.2415120140726773</v>
       </c>
       <c r="G42">
-        <v>0.1624456611808835</v>
+        <v>0.2409390740710613</v>
       </c>
       <c r="H42">
-        <v>0.1353939295158605</v>
+        <v>0.2484685633015908</v>
       </c>
       <c r="I42">
-        <v>0.1672291425197678</v>
+        <v>0.3279026783408415</v>
       </c>
       <c r="J42">
-        <v>0.2150293422566958</v>
+        <v>0.385406448487009</v>
       </c>
       <c r="K42">
-        <v>0.2497645986932844</v>
+        <v>0.4730730369362598</v>
       </c>
       <c r="L42">
-        <v>0.2736633260980973</v>
+        <v>0.5175081304189848</v>
       </c>
       <c r="M42">
-        <v>0.3283727440567289</v>
+        <v>0.5505214388664785</v>
       </c>
       <c r="N42">
-        <v>0.3880293426987568</v>
+        <v>0.5810699723517849</v>
       </c>
       <c r="O42">
-        <v>0.456995210419276</v>
+        <v>0.6132238954938547</v>
       </c>
       <c r="P42">
-        <v>0.5245707091667495</v>
+        <v>0.6543674622346893</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
+          <t>snv_sder_c(1,3,9)_red_c(10,10,1)_</t>
         </is>
       </c>
       <c r="B43">
-        <v>0.02822536472010895</v>
+        <v>0.03552039669765128</v>
       </c>
       <c r="C43">
-        <v>0.1014887398648686</v>
+        <v>0.1062960765777511</v>
       </c>
       <c r="D43">
-        <v>0.05970755811042416</v>
+        <v>0.1498949855538461</v>
       </c>
       <c r="E43">
-        <v>0.06885233581203365</v>
+        <v>0.2264657223581012</v>
       </c>
       <c r="F43">
-        <v>0.09403195258496222</v>
+        <v>0.3663908743678608</v>
       </c>
       <c r="G43">
-        <v>0.1386156954774042</v>
+        <v>0.391396496826124</v>
       </c>
       <c r="H43">
-        <v>0.1264172281056268</v>
+        <v>0.3176747020470456</v>
       </c>
       <c r="I43">
-        <v>0.1581355303365224</v>
+        <v>0.3282062737315229</v>
       </c>
       <c r="J43">
-        <v>0.2058480259115085</v>
+        <v>0.3846566523999077</v>
       </c>
       <c r="K43">
-        <v>0.2582702875765093</v>
+        <v>0.47799700233079</v>
       </c>
       <c r="L43">
-        <v>0.294300889646169</v>
+        <v>0.5242515928360367</v>
       </c>
       <c r="M43">
-        <v>0.3742373217967828</v>
+        <v>0.5576291274538141</v>
       </c>
       <c r="N43">
-        <v>0.4098761635622749</v>
+        <v>0.5745013861292626</v>
       </c>
       <c r="O43">
-        <v>0.4404630132405721</v>
+        <v>0.5798353012829967</v>
       </c>
       <c r="P43">
-        <v>0.4928186312615779</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(2,3,21)_</t>
-        </is>
-      </c>
-      <c r="B44">
-        <v>0.033464897062078</v>
-      </c>
-      <c r="C44">
-        <v>0.06234482230259508</v>
-      </c>
-      <c r="D44">
-        <v>0.09132677487113172</v>
-      </c>
-      <c r="E44">
-        <v>0.1035696284572728</v>
-      </c>
-      <c r="F44">
-        <v>0.129769687677024</v>
-      </c>
-      <c r="G44">
-        <v>0.1568602737091465</v>
-      </c>
-      <c r="H44">
-        <v>0.2156731550664198</v>
-      </c>
-      <c r="I44">
-        <v>0.2468554757579094</v>
-      </c>
-      <c r="J44">
-        <v>0.2878454142660121</v>
-      </c>
-      <c r="K44">
-        <v>0.3524921671894462</v>
-      </c>
-      <c r="L44">
-        <v>0.4395500867850628</v>
-      </c>
-      <c r="M44">
-        <v>0.5360266788366168</v>
-      </c>
-      <c r="N44">
-        <v>0.6061323963957561</v>
-      </c>
-      <c r="O44">
-        <v>0.6896520107462731</v>
-      </c>
-      <c r="P44">
-        <v>0.7704583571308777</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>adj_snv_sder_c(1,3,5)_</t>
-        </is>
-      </c>
-      <c r="B45">
-        <v>0.04071891039006986</v>
-      </c>
-      <c r="C45">
-        <v>0.06452128123790268</v>
-      </c>
-      <c r="D45">
-        <v>0.1560498354825868</v>
-      </c>
-      <c r="E45">
-        <v>0.2586346077308677</v>
-      </c>
-      <c r="F45">
-        <v>0.3830735354241279</v>
-      </c>
-      <c r="G45">
-        <v>0.426594163825658</v>
-      </c>
-      <c r="H45">
-        <v>0.4051123975643586</v>
-      </c>
-      <c r="I45">
-        <v>0.4115288157860641</v>
-      </c>
-      <c r="J45">
-        <v>0.4357233176960568</v>
-      </c>
-      <c r="K45">
-        <v>0.5074897128241274</v>
-      </c>
-      <c r="L45">
-        <v>0.6159945055432314</v>
-      </c>
-      <c r="M45">
-        <v>0.6844522823647415</v>
-      </c>
-      <c r="N45">
-        <v>0.742923940058603</v>
-      </c>
-      <c r="O45">
-        <v>0.8025762973681543</v>
-      </c>
-      <c r="P45">
-        <v>0.8146618728672678</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>adj_snv_sder_c(2,3,15)_</t>
-        </is>
-      </c>
-      <c r="B46">
-        <v>0.04456598188450372</v>
-      </c>
-      <c r="C46">
-        <v>0.04781881448075287</v>
-      </c>
-      <c r="D46">
-        <v>0.1259879787446392</v>
-      </c>
-      <c r="E46">
-        <v>0.1657191073469815</v>
-      </c>
-      <c r="F46">
-        <v>0.2355009623172741</v>
-      </c>
-      <c r="G46">
-        <v>0.2339144678488333</v>
-      </c>
-      <c r="H46">
-        <v>0.2413250037854349</v>
-      </c>
-      <c r="I46">
-        <v>0.3169816170560619</v>
-      </c>
-      <c r="J46">
-        <v>0.3740453460718787</v>
-      </c>
-      <c r="K46">
-        <v>0.463392372112455</v>
-      </c>
-      <c r="L46">
-        <v>0.5032268295289783</v>
-      </c>
-      <c r="M46">
-        <v>0.5374521297236149</v>
-      </c>
-      <c r="N46">
-        <v>0.5674041282227686</v>
-      </c>
-      <c r="O46">
-        <v>0.6037161752601597</v>
-      </c>
-      <c r="P46">
-        <v>0.6383513012025772</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>snv_sder_c(1,3,9)_red_c(10,10,1)_</t>
-        </is>
-      </c>
-      <c r="B47">
-        <v>0.03199320361235436</v>
-      </c>
-      <c r="C47">
-        <v>0.1003839728586005</v>
-      </c>
-      <c r="D47">
-        <v>0.1421556861827729</v>
-      </c>
-      <c r="E47">
-        <v>0.2183999474424864</v>
-      </c>
-      <c r="F47">
-        <v>0.3611905691083123</v>
-      </c>
-      <c r="G47">
-        <v>0.381533257709403</v>
-      </c>
-      <c r="H47">
-        <v>0.314539981931479</v>
-      </c>
-      <c r="I47">
-        <v>0.3217404381422787</v>
-      </c>
-      <c r="J47">
-        <v>0.3735555132051305</v>
-      </c>
-      <c r="K47">
-        <v>0.4696856945905256</v>
-      </c>
-      <c r="L47">
-        <v>0.5150438377524462</v>
-      </c>
-      <c r="M47">
-        <v>0.5459837240219951</v>
-      </c>
-      <c r="N47">
-        <v>0.5576657089306283</v>
-      </c>
-      <c r="O47">
-        <v>0.5607985253010529</v>
-      </c>
-      <c r="P47">
-        <v>0.5702751941914947</v>
+        <v>0.584308747674526</v>
       </c>
     </row>
   </sheetData>
